--- a/testbuild/StructureDefinition-vkp-Observation-CFSscore.xlsx
+++ b/testbuild/StructureDefinition-vkp-Observation-CFSscore.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$131</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$135</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5047" uniqueCount="733">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5199" uniqueCount="705">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.2</t>
+    <t>0.6.0-alpha</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T11:31:28+00:00</t>
+    <t>2026-10-02T06:31:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1450,7 +1450,7 @@
 </t>
   </si>
   <si>
-    <t>Reference to the author of the observation</t>
+    <t>A reference to the author of the observation. Usually an identified Practitioner but can just as likely be an identified role/locations/specialties/services within an organization identified by a PractitionerRole or CareTeam</t>
   </si>
   <si>
     <t>Reference to the person, role or team that performed the observation, identified by Norwegian national id number (Fødselsnummer or DNR).
@@ -1493,9 +1493,6 @@
     <t>Observation.performer.type</t>
   </si>
   <si>
-    <t>http://hl7.no/fhir/vkpobservation/ValueSet/vkp-performer-reference-types.valueset</t>
-  </si>
-  <si>
     <t>Observation.performer:author.identifier</t>
   </si>
   <si>
@@ -1659,163 +1656,79 @@
     <t>363714003 |Interprets|</t>
   </si>
   <si>
-    <t>Observation.value[x]:valueQuantity</t>
-  </si>
-  <si>
-    <t>valueQuantity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantity
-</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueQuantity.id</t>
+    <t>Observation.value[x]:valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueCodeableConcept.id</t>
   </si>
   <si>
     <t>Observation.value[x].id</t>
   </si>
   <si>
-    <t>Observation.value[x]:valueQuantity.extension</t>
+    <t>Observation.value[x]:valueCodeableConcept.extension</t>
   </si>
   <si>
     <t>Observation.value[x].extension</t>
   </si>
   <si>
-    <t>Observation.value[x]:valueQuantity.value</t>
-  </si>
-  <si>
-    <t>Observation.value[x].value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">decimal
-</t>
-  </si>
-  <si>
-    <t>Numerical value (with implicit precision)</t>
-  </si>
-  <si>
-    <t>The value of the measured amount. The value includes an implicit precision in the presentation of the value.</t>
-  </si>
-  <si>
-    <t>The implicit precision in the value should always be honored. Monetary values have their own rules for handling precision (refer to standard accounting text books).</t>
-  </si>
-  <si>
-    <t>Precision is handled implicitly in almost all cases of measurement.</t>
-  </si>
-  <si>
-    <t>Quantity.value</t>
-  </si>
-  <si>
-    <t>SN.2  / CQ - N/A</t>
-  </si>
-  <si>
-    <t>PQ.value, CO.value, MO.value, IVL.high or IVL.low depending on the value</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueQuantity.comparator</t>
-  </si>
-  <si>
-    <t>Observation.value[x].comparator</t>
-  </si>
-  <si>
-    <t>&lt; | &lt;= | &gt;= | &gt; - how to understand the value</t>
-  </si>
-  <si>
-    <t>How the value should be understood and represented - whether the actual value is greater or less than the stated value due to measurement issues; e.g. if the comparator is "&lt;" , then the real value is &lt; stated value.</t>
-  </si>
-  <si>
-    <t>Need a framework for handling measures where the value is &lt;5ug/L or &gt;400mg/L due to the limitations of measuring methodology.</t>
-  </si>
-  <si>
-    <t>If there is no comparator, then there is no modification of the value</t>
-  </si>
-  <si>
-    <t>How the Quantity should be understood and represented.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/quantity-comparator|4.0.1</t>
-  </si>
-  <si>
-    <t>Quantity.comparator</t>
-  </si>
-  <si>
-    <t>SN.1  / CQ.1</t>
-  </si>
-  <si>
-    <t>IVL properties</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueQuantity.unit</t>
-  </si>
-  <si>
-    <t>Observation.value[x].unit</t>
-  </si>
-  <si>
-    <t>Unit representation</t>
-  </si>
-  <si>
-    <t>A human-readable form of the unit.</t>
-  </si>
-  <si>
-    <t>There are many representations for units of measure and in many contexts, particular representations are fixed and required. I.e. mcg for micrograms.</t>
-  </si>
-  <si>
-    <t>Quantity.unit</t>
-  </si>
-  <si>
-    <t>(see OBX.6 etc.) / CQ.2</t>
-  </si>
-  <si>
-    <t>PQ.unit</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueQuantity.system</t>
-  </si>
-  <si>
-    <t>Observation.value[x].system</t>
-  </si>
-  <si>
-    <t>System that defines coded unit form</t>
-  </si>
-  <si>
-    <t>The identification of the system that provides the coded form of the unit.</t>
-  </si>
-  <si>
-    <t>Need to know the system that defines the coded form of the unit.</t>
-  </si>
-  <si>
-    <t>Quantity.system</t>
-  </si>
-  <si>
-    <t xml:space="preserve">qty-3
-</t>
-  </si>
-  <si>
-    <t>CO.codeSystem, PQ.translation.codeSystem</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueQuantity.code</t>
-  </si>
-  <si>
-    <t>Observation.value[x].code</t>
-  </si>
-  <si>
-    <t>Coded form of the unit</t>
-  </si>
-  <si>
-    <t>A computer processable form of the unit in some unit representation system.</t>
-  </si>
-  <si>
-    <t>The preferred system is UCUM, but SNOMED CT can also be used (for customary units) or ISO 4217 for currency.  The context of use may additionally require a code from a particular system.</t>
-  </si>
-  <si>
-    <t>Need a computable form of the unit that is fixed across all forms. UCUM provides this for quantities, but SNOMED CT provides many units of interest.</t>
-  </si>
-  <si>
-    <t>Quantity.code</t>
-  </si>
-  <si>
-    <t>PQ.code, MO.currency, PQ.translation.code</t>
+    <t>Observation.value[x]:valueCodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>Observation.value[x].coding</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueCodeableConcept.coding.id</t>
+  </si>
+  <si>
+    <t>Observation.value[x].coding.id</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueCodeableConcept.coding.extension</t>
+  </si>
+  <si>
+    <t>Observation.value[x].coding.extension</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueCodeableConcept.coding.system</t>
+  </si>
+  <si>
+    <t>Observation.value[x].coding.system</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueCodeableConcept.coding.version</t>
+  </si>
+  <si>
+    <t>Observation.value[x].coding.version</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueCodeableConcept.coding.code</t>
+  </si>
+  <si>
+    <t>Observation.value[x].coding.code</t>
+  </si>
+  <si>
+    <t>http://hl7.no/fhir/vkpobservation/ValueSet/vkp-cfs-score.valueset</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueCodeableConcept.coding.display</t>
+  </si>
+  <si>
+    <t>Observation.value[x].coding.display</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueCodeableConcept.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Observation.value[x].coding.userSelected</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueCodeableConcept.text</t>
+  </si>
+  <si>
+    <t>Observation.value[x].text</t>
   </si>
   <si>
     <t>Observation.dataAbsentReason</t>
@@ -2635,12 +2548,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP131"/>
+  <dimension ref="A1:AP135"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="44.95703125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="52.62109375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="38.30078125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.98046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="19.078125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -10940,11 +10853,13 @@
         <v>83</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="Y69" s="2"/>
+        <v>341</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>342</v>
+      </c>
       <c r="Z69" t="s" s="2">
-        <v>468</v>
+        <v>343</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>83</v>
@@ -10997,10 +10912,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B70" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>470</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11117,10 +11032,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="B71" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>472</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11235,10 +11150,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="B72" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11355,10 +11270,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="B73" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>476</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11477,10 +11392,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="B74" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11599,10 +11514,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="B75" t="s" s="2">
         <v>479</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>480</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11666,7 +11581,7 @@
       </c>
       <c r="Y75" s="2"/>
       <c r="Z75" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>83</v>
@@ -11719,10 +11634,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="B76" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>483</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11839,10 +11754,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="B77" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>485</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11957,10 +11872,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="B78" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="B78" t="s" s="2">
-        <v>487</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12077,10 +11992,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="B79" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>489</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12197,13 +12112,13 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>445</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D80" t="s" s="2">
         <v>83</v>
@@ -12225,13 +12140,13 @@
         <v>95</v>
       </c>
       <c r="K80" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="L80" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="L80" t="s" s="2">
+      <c r="M80" t="s" s="2">
         <v>493</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>494</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
@@ -12319,7 +12234,7 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B81" t="s" s="2">
         <v>461</v>
@@ -12437,7 +12352,7 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B82" t="s" s="2">
         <v>463</v>
@@ -12557,7 +12472,7 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B83" t="s" s="2">
         <v>465</v>
@@ -12677,7 +12592,7 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B84" t="s" s="2">
         <v>467</v>
@@ -12797,10 +12712,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12917,10 +12832,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13035,10 +12950,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13155,10 +13070,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13277,10 +13192,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13399,10 +13314,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13466,7 +13381,7 @@
       </c>
       <c r="Y90" s="2"/>
       <c r="Z90" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>83</v>
@@ -13519,10 +13434,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13639,10 +13554,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13757,10 +13672,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13877,10 +13792,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13997,10 +13912,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14023,19 +13938,19 @@
         <v>95</v>
       </c>
       <c r="K95" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="L95" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="L95" t="s" s="2">
+      <c r="M95" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="M95" t="s" s="2">
+      <c r="N95" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="N95" t="s" s="2">
+      <c r="O95" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>515</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>83</v>
@@ -14072,7 +13987,7 @@
         <v>83</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="AC95" s="2"/>
       <c r="AD95" t="s" s="2">
@@ -14082,7 +13997,7 @@
         <v>226</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -14091,7 +14006,7 @@
         <v>94</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>106</v>
@@ -14100,30 +14015,30 @@
         <v>83</v>
       </c>
       <c r="AL95" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="AM95" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="AM95" t="s" s="2">
+      <c r="AN95" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="AN95" t="s" s="2">
+      <c r="AO95" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP95" t="s" s="2">
         <v>520</v>
-      </c>
-      <c r="AO95" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP95" t="s" s="2">
-        <v>521</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="C96" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="B96" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="C96" t="s" s="2">
-        <v>523</v>
       </c>
       <c r="D96" t="s" s="2">
         <v>83</v>
@@ -14145,19 +14060,19 @@
         <v>95</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>524</v>
+        <v>192</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="M96" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="M96" t="s" s="2">
+      <c r="N96" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="N96" t="s" s="2">
+      <c r="O96" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>515</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>83</v>
@@ -14206,7 +14121,7 @@
         <v>83</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -14215,7 +14130,7 @@
         <v>94</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AJ96" t="s" s="2">
         <v>106</v>
@@ -14224,27 +14139,27 @@
         <v>83</v>
       </c>
       <c r="AL96" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="AM96" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="AM96" t="s" s="2">
+      <c r="AN96" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="AN96" t="s" s="2">
+      <c r="AO96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP96" t="s" s="2">
         <v>520</v>
-      </c>
-      <c r="AO96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP96" t="s" s="2">
-        <v>521</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14359,10 +14274,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14477,12 +14392,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14493,10 +14408,10 @@
         <v>81</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H99" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I99" t="s" s="2">
         <v>83</v>
@@ -14505,19 +14420,19 @@
         <v>95</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>531</v>
+        <v>229</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>532</v>
+        <v>230</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>533</v>
+        <v>231</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>534</v>
+        <v>232</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>535</v>
+        <v>233</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>83</v>
@@ -14566,13 +14481,13 @@
         <v>83</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>536</v>
+        <v>236</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>83</v>
@@ -14587,10 +14502,10 @@
         <v>83</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>537</v>
+        <v>237</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>538</v>
+        <v>238</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>83</v>
@@ -14601,10 +14516,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>539</v>
+        <v>529</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>540</v>
+        <v>530</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14621,30 +14536,26 @@
         <v>83</v>
       </c>
       <c r="I100" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>114</v>
+        <v>217</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>541</v>
+        <v>218</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>542</v>
+        <v>219</v>
       </c>
       <c r="N100" s="2"/>
-      <c r="O100" t="s" s="2">
-        <v>543</v>
-      </c>
+      <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="Q100" t="s" s="2">
-        <v>544</v>
-      </c>
+      <c r="Q100" s="2"/>
       <c r="R100" t="s" s="2">
         <v>83</v>
       </c>
@@ -14664,13 +14575,13 @@
         <v>83</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>183</v>
+        <v>83</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>545</v>
+        <v>83</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>546</v>
+        <v>83</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>83</v>
@@ -14688,7 +14599,7 @@
         <v>83</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>547</v>
+        <v>220</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
@@ -14700,7 +14611,7 @@
         <v>83</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>83</v>
@@ -14709,10 +14620,10 @@
         <v>83</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>548</v>
+        <v>83</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>549</v>
+        <v>221</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>83</v>
@@ -14723,21 +14634,21 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>550</v>
+        <v>531</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>551</v>
+        <v>532</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>83</v>
@@ -14746,21 +14657,21 @@
         <v>83</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>217</v>
+        <v>140</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>552</v>
+        <v>141</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="N101" s="2"/>
-      <c r="O101" t="s" s="2">
-        <v>554</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>83</v>
       </c>
@@ -14796,31 +14707,31 @@
         <v>83</v>
       </c>
       <c r="AB101" t="s" s="2">
-        <v>83</v>
+        <v>224</v>
       </c>
       <c r="AC101" t="s" s="2">
-        <v>83</v>
+        <v>225</v>
       </c>
       <c r="AD101" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>83</v>
+        <v>226</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>555</v>
+        <v>227</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>83</v>
@@ -14829,10 +14740,10 @@
         <v>83</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>556</v>
+        <v>83</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>557</v>
+        <v>221</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>83</v>
@@ -14843,10 +14754,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>558</v>
+        <v>533</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>559</v>
+        <v>534</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14872,14 +14783,16 @@
         <v>108</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>560</v>
+        <v>247</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="N102" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>249</v>
+      </c>
       <c r="O102" t="s" s="2">
-        <v>562</v>
+        <v>250</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>83</v>
@@ -14928,7 +14841,7 @@
         <v>83</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>563</v>
+        <v>252</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
@@ -14937,7 +14850,7 @@
         <v>94</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>564</v>
+        <v>83</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>106</v>
@@ -14949,10 +14862,10 @@
         <v>83</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>556</v>
+        <v>253</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>565</v>
+        <v>254</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>83</v>
@@ -14963,10 +14876,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>566</v>
+        <v>535</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>567</v>
+        <v>536</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14989,20 +14902,18 @@
         <v>95</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>114</v>
+        <v>217</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>568</v>
+        <v>257</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>569</v>
+        <v>258</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>571</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>83</v>
       </c>
@@ -15050,7 +14961,7 @@
         <v>83</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>572</v>
+        <v>260</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>81</v>
@@ -15071,10 +14982,10 @@
         <v>83</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>556</v>
+        <v>261</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>573</v>
+        <v>262</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>83</v>
@@ -15085,10 +14996,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>574</v>
+        <v>537</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>574</v>
+        <v>538</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15108,22 +15019,20 @@
         <v>83</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>192</v>
+        <v>114</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>575</v>
+        <v>265</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>577</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="N104" s="2"/>
       <c r="O104" t="s" s="2">
-        <v>578</v>
+        <v>267</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>83</v>
@@ -15148,13 +15057,11 @@
         <v>83</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="Y104" t="s" s="2">
-        <v>579</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="Y104" s="2"/>
       <c r="Z104" t="s" s="2">
-        <v>580</v>
+        <v>539</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>83</v>
@@ -15172,7 +15079,7 @@
         <v>83</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>574</v>
+        <v>268</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>81</v>
@@ -15181,7 +15088,7 @@
         <v>94</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>581</v>
+        <v>83</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>106</v>
@@ -15193,10 +15100,10 @@
         <v>83</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>137</v>
+        <v>269</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>582</v>
+        <v>270</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>83</v>
@@ -15207,21 +15114,21 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>583</v>
+        <v>540</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>583</v>
+        <v>541</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>584</v>
+        <v>83</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>83</v>
@@ -15230,22 +15137,20 @@
         <v>83</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>585</v>
+        <v>273</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>587</v>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="N105" s="2"/>
       <c r="O105" t="s" s="2">
-        <v>588</v>
+        <v>275</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>83</v>
@@ -15270,13 +15175,13 @@
         <v>83</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>341</v>
+        <v>83</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>589</v>
+        <v>83</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>590</v>
+        <v>83</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>83</v>
@@ -15294,13 +15199,13 @@
         <v>83</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>583</v>
+        <v>276</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>83</v>
@@ -15312,27 +15217,27 @@
         <v>83</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>591</v>
+        <v>83</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>592</v>
+        <v>277</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>593</v>
+        <v>278</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP105" t="s" s="2">
-        <v>594</v>
+        <v>83</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>595</v>
+        <v>542</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>595</v>
+        <v>543</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15343,31 +15248,31 @@
         <v>81</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J106" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="I106" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J106" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="K106" t="s" s="2">
-        <v>596</v>
+        <v>281</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>597</v>
+        <v>282</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>598</v>
+        <v>283</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>599</v>
+        <v>284</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>600</v>
+        <v>285</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>83</v>
@@ -15416,13 +15321,13 @@
         <v>83</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>595</v>
+        <v>286</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>83</v>
@@ -15437,10 +15342,10 @@
         <v>83</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>601</v>
+        <v>287</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>602</v>
+        <v>288</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>83</v>
@@ -15451,10 +15356,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>603</v>
+        <v>544</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>603</v>
+        <v>545</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15474,21 +15379,23 @@
         <v>83</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>604</v>
+        <v>312</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>605</v>
+        <v>313</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="O107" s="2"/>
+        <v>314</v>
+      </c>
+      <c r="O107" t="s" s="2">
+        <v>315</v>
+      </c>
       <c r="P107" t="s" s="2">
         <v>83</v>
       </c>
@@ -15512,13 +15419,13 @@
         <v>83</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>207</v>
+        <v>83</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>607</v>
+        <v>83</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>608</v>
+        <v>83</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>83</v>
@@ -15536,7 +15443,7 @@
         <v>83</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>603</v>
+        <v>316</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
@@ -15554,27 +15461,27 @@
         <v>83</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>609</v>
+        <v>83</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>610</v>
+        <v>317</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>611</v>
+        <v>318</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP107" t="s" s="2">
-        <v>612</v>
+        <v>83</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>613</v>
+        <v>546</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>613</v>
+        <v>546</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15600,16 +15507,16 @@
         <v>192</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>614</v>
+        <v>547</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>615</v>
+        <v>548</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>616</v>
+        <v>549</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>617</v>
+        <v>550</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>83</v>
@@ -15634,13 +15541,13 @@
         <v>83</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>207</v>
+        <v>341</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>618</v>
+        <v>551</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>619</v>
+        <v>552</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>83</v>
@@ -15658,7 +15565,7 @@
         <v>83</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>613</v>
+        <v>546</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
@@ -15667,7 +15574,7 @@
         <v>94</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>83</v>
+        <v>553</v>
       </c>
       <c r="AJ108" t="s" s="2">
         <v>106</v>
@@ -15679,10 +15586,10 @@
         <v>83</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>620</v>
+        <v>137</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>621</v>
+        <v>554</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>83</v>
@@ -15693,21 +15600,21 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>622</v>
+        <v>555</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>622</v>
+        <v>555</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>83</v>
+        <v>556</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>83</v>
@@ -15719,18 +15626,20 @@
         <v>83</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>623</v>
+        <v>192</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>624</v>
+        <v>557</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>625</v>
+        <v>558</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="O109" s="2"/>
+        <v>559</v>
+      </c>
+      <c r="O109" t="s" s="2">
+        <v>560</v>
+      </c>
       <c r="P109" t="s" s="2">
         <v>83</v>
       </c>
@@ -15754,13 +15663,13 @@
         <v>83</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>83</v>
+        <v>341</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>83</v>
+        <v>561</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>83</v>
+        <v>562</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>83</v>
@@ -15778,13 +15687,13 @@
         <v>83</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>622</v>
+        <v>555</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>83</v>
@@ -15796,27 +15705,27 @@
         <v>83</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>627</v>
+        <v>563</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>628</v>
+        <v>564</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>629</v>
+        <v>565</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP109" t="s" s="2">
-        <v>630</v>
+        <v>566</v>
       </c>
     </row>
-    <row r="110" hidden="true">
+    <row r="110">
       <c r="A110" t="s" s="2">
-        <v>631</v>
+        <v>567</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>631</v>
+        <v>567</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15827,10 +15736,10 @@
         <v>81</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H110" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I110" t="s" s="2">
         <v>83</v>
@@ -15839,18 +15748,20 @@
         <v>83</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>632</v>
+        <v>568</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>633</v>
+        <v>569</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>634</v>
+        <v>570</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="O110" s="2"/>
+        <v>571</v>
+      </c>
+      <c r="O110" t="s" s="2">
+        <v>572</v>
+      </c>
       <c r="P110" t="s" s="2">
         <v>83</v>
       </c>
@@ -15898,13 +15809,13 @@
         <v>83</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>631</v>
+        <v>567</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>83</v>
@@ -15916,27 +15827,27 @@
         <v>83</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>636</v>
+        <v>83</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>637</v>
+        <v>573</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>638</v>
+        <v>574</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP110" t="s" s="2">
-        <v>639</v>
+        <v>83</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>640</v>
+        <v>575</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>640</v>
+        <v>575</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15947,7 +15858,7 @@
         <v>81</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>83</v>
@@ -15959,20 +15870,18 @@
         <v>83</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>641</v>
+        <v>192</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>642</v>
+        <v>576</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>643</v>
+        <v>577</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="O111" t="s" s="2">
-        <v>645</v>
-      </c>
+        <v>578</v>
+      </c>
+      <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>83</v>
       </c>
@@ -15996,13 +15905,13 @@
         <v>83</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>83</v>
+        <v>207</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>83</v>
+        <v>579</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>83</v>
+        <v>580</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>83</v>
@@ -16020,45 +15929,45 @@
         <v>83</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>640</v>
+        <v>575</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>646</v>
+        <v>106</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>83</v>
+        <v>581</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>647</v>
+        <v>582</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>648</v>
+        <v>583</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP111" t="s" s="2">
-        <v>83</v>
+        <v>584</v>
       </c>
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>649</v>
+        <v>585</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>649</v>
+        <v>585</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16081,16 +15990,20 @@
         <v>83</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>217</v>
+        <v>192</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>218</v>
+        <v>586</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N112" s="2"/>
-      <c r="O112" s="2"/>
+        <v>587</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="O112" t="s" s="2">
+        <v>589</v>
+      </c>
       <c r="P112" t="s" s="2">
         <v>83</v>
       </c>
@@ -16114,13 +16027,13 @@
         <v>83</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>83</v>
+        <v>207</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>83</v>
+        <v>590</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>83</v>
+        <v>591</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>83</v>
@@ -16138,7 +16051,7 @@
         <v>83</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>220</v>
+        <v>585</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>81</v>
@@ -16150,7 +16063,7 @@
         <v>83</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK112" t="s" s="2">
         <v>83</v>
@@ -16159,10 +16072,10 @@
         <v>83</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>83</v>
+        <v>592</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>221</v>
+        <v>593</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>83</v>
@@ -16173,21 +16086,21 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>650</v>
+        <v>594</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>650</v>
+        <v>594</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>83</v>
@@ -16199,16 +16112,16 @@
         <v>83</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>140</v>
+        <v>595</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>141</v>
+        <v>596</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>223</v>
+        <v>597</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>143</v>
+        <v>598</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -16258,81 +16171,79 @@
         <v>83</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>227</v>
+        <v>594</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>83</v>
+        <v>599</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>83</v>
+        <v>600</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>221</v>
+        <v>601</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP113" t="s" s="2">
-        <v>83</v>
+        <v>602</v>
       </c>
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>651</v>
+        <v>603</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>651</v>
+        <v>603</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>652</v>
+        <v>83</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I114" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J114" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>140</v>
+        <v>604</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>653</v>
+        <v>605</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>654</v>
+        <v>606</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O114" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>607</v>
+      </c>
+      <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
         <v>83</v>
       </c>
@@ -16380,45 +16291,45 @@
         <v>83</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>655</v>
+        <v>603</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK114" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>83</v>
+        <v>608</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>83</v>
+        <v>609</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>137</v>
+        <v>610</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP114" t="s" s="2">
-        <v>83</v>
+        <v>611</v>
       </c>
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>656</v>
+        <v>612</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>656</v>
+        <v>612</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16429,7 +16340,7 @@
         <v>81</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>83</v>
@@ -16441,16 +16352,20 @@
         <v>83</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>657</v>
+        <v>613</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>658</v>
+        <v>614</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="N115" s="2"/>
-      <c r="O115" s="2"/>
+        <v>615</v>
+      </c>
+      <c r="N115" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="O115" t="s" s="2">
+        <v>617</v>
+      </c>
       <c r="P115" t="s" s="2">
         <v>83</v>
       </c>
@@ -16498,19 +16413,19 @@
         <v>83</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>656</v>
+        <v>612</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI115" t="s" s="2">
-        <v>660</v>
+        <v>83</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>106</v>
+        <v>618</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>83</v>
@@ -16519,10 +16434,10 @@
         <v>83</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>661</v>
+        <v>619</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>662</v>
+        <v>620</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>83</v>
@@ -16533,10 +16448,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>663</v>
+        <v>621</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>663</v>
+        <v>621</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16559,13 +16474,13 @@
         <v>83</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>657</v>
+        <v>217</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>664</v>
+        <v>218</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>665</v>
+        <v>219</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -16616,7 +16531,7 @@
         <v>83</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>663</v>
+        <v>220</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>81</v>
@@ -16625,10 +16540,10 @@
         <v>94</v>
       </c>
       <c r="AI116" t="s" s="2">
-        <v>660</v>
+        <v>83</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK116" t="s" s="2">
         <v>83</v>
@@ -16637,10 +16552,10 @@
         <v>83</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>661</v>
+        <v>83</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>666</v>
+        <v>221</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>83</v>
@@ -16651,21 +16566,21 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>667</v>
+        <v>622</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>667</v>
+        <v>622</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>83</v>
@@ -16677,20 +16592,18 @@
         <v>83</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>192</v>
+        <v>140</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>668</v>
+        <v>141</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>669</v>
+        <v>223</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>670</v>
-      </c>
-      <c r="O117" t="s" s="2">
-        <v>671</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
         <v>83</v>
       </c>
@@ -16714,13 +16627,13 @@
         <v>83</v>
       </c>
       <c r="X117" t="s" s="2">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>672</v>
+        <v>83</v>
       </c>
       <c r="Z117" t="s" s="2">
-        <v>673</v>
+        <v>83</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>83</v>
@@ -16738,31 +16651,31 @@
         <v>83</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>667</v>
+        <v>227</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI117" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>674</v>
+        <v>83</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>675</v>
+        <v>83</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>593</v>
+        <v>221</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>83</v>
@@ -16773,14 +16686,14 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>676</v>
+        <v>623</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>676</v>
+        <v>623</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>83</v>
+        <v>624</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
@@ -16793,25 +16706,25 @@
         <v>83</v>
       </c>
       <c r="I118" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J118" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>192</v>
+        <v>140</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>677</v>
+        <v>625</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>678</v>
+        <v>626</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>679</v>
+        <v>143</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>680</v>
+        <v>149</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>83</v>
@@ -16836,13 +16749,13 @@
         <v>83</v>
       </c>
       <c r="X118" t="s" s="2">
-        <v>207</v>
+        <v>83</v>
       </c>
       <c r="Y118" t="s" s="2">
-        <v>681</v>
+        <v>83</v>
       </c>
       <c r="Z118" t="s" s="2">
-        <v>682</v>
+        <v>83</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>83</v>
@@ -16860,7 +16773,7 @@
         <v>83</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>676</v>
+        <v>627</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>81</v>
@@ -16872,19 +16785,19 @@
         <v>83</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>674</v>
+        <v>83</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>675</v>
+        <v>83</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>593</v>
+        <v>137</v>
       </c>
       <c r="AO118" t="s" s="2">
         <v>83</v>
@@ -16895,10 +16808,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>683</v>
+        <v>628</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>683</v>
+        <v>628</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16921,18 +16834,16 @@
         <v>83</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>684</v>
+        <v>629</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>685</v>
+        <v>630</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>686</v>
+        <v>631</v>
       </c>
       <c r="N119" s="2"/>
-      <c r="O119" t="s" s="2">
-        <v>687</v>
-      </c>
+      <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>83</v>
       </c>
@@ -16980,7 +16891,7 @@
         <v>83</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>683</v>
+        <v>628</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>81</v>
@@ -16989,7 +16900,7 @@
         <v>94</v>
       </c>
       <c r="AI119" t="s" s="2">
-        <v>83</v>
+        <v>632</v>
       </c>
       <c r="AJ119" t="s" s="2">
         <v>106</v>
@@ -17001,10 +16912,10 @@
         <v>83</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>83</v>
+        <v>633</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>688</v>
+        <v>634</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>83</v>
@@ -17015,10 +16926,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>689</v>
+        <v>635</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>689</v>
+        <v>635</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17041,13 +16952,13 @@
         <v>83</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>217</v>
+        <v>629</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>690</v>
+        <v>636</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>691</v>
+        <v>637</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -17098,7 +17009,7 @@
         <v>83</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>689</v>
+        <v>635</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>81</v>
@@ -17107,7 +17018,7 @@
         <v>94</v>
       </c>
       <c r="AI120" t="s" s="2">
-        <v>83</v>
+        <v>632</v>
       </c>
       <c r="AJ120" t="s" s="2">
         <v>106</v>
@@ -17119,10 +17030,10 @@
         <v>83</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>661</v>
+        <v>633</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>692</v>
+        <v>638</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>83</v>
@@ -17133,10 +17044,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>693</v>
+        <v>639</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>693</v>
+        <v>639</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17147,7 +17058,7 @@
         <v>81</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H121" t="s" s="2">
         <v>83</v>
@@ -17156,21 +17067,23 @@
         <v>83</v>
       </c>
       <c r="J121" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>694</v>
+        <v>192</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>695</v>
+        <v>640</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>696</v>
+        <v>641</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>697</v>
-      </c>
-      <c r="O121" s="2"/>
+        <v>642</v>
+      </c>
+      <c r="O121" t="s" s="2">
+        <v>643</v>
+      </c>
       <c r="P121" t="s" s="2">
         <v>83</v>
       </c>
@@ -17194,13 +17107,13 @@
         <v>83</v>
       </c>
       <c r="X121" t="s" s="2">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="Y121" t="s" s="2">
-        <v>83</v>
+        <v>644</v>
       </c>
       <c r="Z121" t="s" s="2">
-        <v>83</v>
+        <v>645</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>83</v>
@@ -17218,13 +17131,13 @@
         <v>83</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>693</v>
+        <v>639</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI121" t="s" s="2">
         <v>83</v>
@@ -17236,13 +17149,13 @@
         <v>83</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>83</v>
+        <v>646</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>698</v>
+        <v>647</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>699</v>
+        <v>565</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>83</v>
@@ -17253,10 +17166,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>700</v>
+        <v>648</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>700</v>
+        <v>648</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17276,21 +17189,23 @@
         <v>83</v>
       </c>
       <c r="J122" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>701</v>
+        <v>192</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>702</v>
+        <v>649</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>703</v>
+        <v>650</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>704</v>
-      </c>
-      <c r="O122" s="2"/>
+        <v>651</v>
+      </c>
+      <c r="O122" t="s" s="2">
+        <v>652</v>
+      </c>
       <c r="P122" t="s" s="2">
         <v>83</v>
       </c>
@@ -17314,13 +17229,13 @@
         <v>83</v>
       </c>
       <c r="X122" t="s" s="2">
-        <v>83</v>
+        <v>207</v>
       </c>
       <c r="Y122" t="s" s="2">
-        <v>83</v>
+        <v>653</v>
       </c>
       <c r="Z122" t="s" s="2">
-        <v>83</v>
+        <v>654</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>83</v>
@@ -17338,7 +17253,7 @@
         <v>83</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>700</v>
+        <v>648</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>81</v>
@@ -17356,13 +17271,13 @@
         <v>83</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>83</v>
+        <v>646</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>698</v>
+        <v>647</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>705</v>
+        <v>565</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>83</v>
@@ -17373,10 +17288,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>706</v>
+        <v>655</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>706</v>
+        <v>655</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17387,7 +17302,7 @@
         <v>81</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H123" t="s" s="2">
         <v>83</v>
@@ -17396,22 +17311,20 @@
         <v>83</v>
       </c>
       <c r="J123" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>641</v>
+        <v>656</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>707</v>
+        <v>657</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>708</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>709</v>
-      </c>
+        <v>658</v>
+      </c>
+      <c r="N123" s="2"/>
       <c r="O123" t="s" s="2">
-        <v>710</v>
+        <v>659</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>83</v>
@@ -17460,13 +17373,13 @@
         <v>83</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>706</v>
+        <v>655</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH123" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI123" t="s" s="2">
         <v>83</v>
@@ -17481,10 +17394,10 @@
         <v>83</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>711</v>
+        <v>83</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>712</v>
+        <v>660</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>83</v>
@@ -17495,10 +17408,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>713</v>
+        <v>661</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>713</v>
+        <v>661</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17524,10 +17437,10 @@
         <v>217</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>218</v>
+        <v>662</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>219</v>
+        <v>663</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -17578,7 +17491,7 @@
         <v>83</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>220</v>
+        <v>661</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>81</v>
@@ -17590,7 +17503,7 @@
         <v>83</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK124" t="s" s="2">
         <v>83</v>
@@ -17599,10 +17512,10 @@
         <v>83</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>83</v>
+        <v>633</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>221</v>
+        <v>664</v>
       </c>
       <c r="AO124" t="s" s="2">
         <v>83</v>
@@ -17613,14 +17526,14 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>714</v>
+        <v>665</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>714</v>
+        <v>665</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
@@ -17636,19 +17549,19 @@
         <v>83</v>
       </c>
       <c r="J125" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>140</v>
+        <v>666</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>141</v>
+        <v>667</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>223</v>
+        <v>668</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>143</v>
+        <v>669</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -17698,7 +17611,7 @@
         <v>83</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>227</v>
+        <v>665</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>81</v>
@@ -17710,7 +17623,7 @@
         <v>83</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK125" t="s" s="2">
         <v>83</v>
@@ -17719,10 +17632,10 @@
         <v>83</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>83</v>
+        <v>670</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>221</v>
+        <v>671</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>83</v>
@@ -17733,14 +17646,14 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>715</v>
+        <v>672</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>715</v>
+        <v>672</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
-        <v>652</v>
+        <v>83</v>
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
@@ -17753,26 +17666,24 @@
         <v>83</v>
       </c>
       <c r="I126" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J126" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>140</v>
+        <v>673</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>653</v>
+        <v>674</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>654</v>
+        <v>675</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O126" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>676</v>
+      </c>
+      <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
         <v>83</v>
       </c>
@@ -17820,7 +17731,7 @@
         <v>83</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>655</v>
+        <v>672</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>81</v>
@@ -17832,7 +17743,7 @@
         <v>83</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK126" t="s" s="2">
         <v>83</v>
@@ -17841,10 +17752,10 @@
         <v>83</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>83</v>
+        <v>670</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>137</v>
+        <v>677</v>
       </c>
       <c r="AO126" t="s" s="2">
         <v>83</v>
@@ -17855,10 +17766,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>716</v>
+        <v>678</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>716</v>
+        <v>678</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17866,10 +17777,10 @@
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G127" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H127" t="s" s="2">
         <v>83</v>
@@ -17881,19 +17792,19 @@
         <v>95</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>192</v>
+        <v>613</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>717</v>
+        <v>679</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>718</v>
+        <v>680</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>719</v>
+        <v>681</v>
       </c>
       <c r="O127" t="s" s="2">
-        <v>206</v>
+        <v>682</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>83</v>
@@ -17918,13 +17829,13 @@
         <v>83</v>
       </c>
       <c r="X127" t="s" s="2">
-        <v>207</v>
+        <v>83</v>
       </c>
       <c r="Y127" t="s" s="2">
-        <v>208</v>
+        <v>83</v>
       </c>
       <c r="Z127" t="s" s="2">
-        <v>209</v>
+        <v>83</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>83</v>
@@ -17942,13 +17853,13 @@
         <v>83</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>716</v>
+        <v>678</v>
       </c>
       <c r="AG127" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH127" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI127" t="s" s="2">
         <v>83</v>
@@ -17960,16 +17871,16 @@
         <v>83</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>720</v>
+        <v>83</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>212</v>
+        <v>683</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>213</v>
+        <v>684</v>
       </c>
       <c r="AO127" t="s" s="2">
-        <v>214</v>
+        <v>83</v>
       </c>
       <c r="AP127" t="s" s="2">
         <v>83</v>
@@ -17977,10 +17888,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>721</v>
+        <v>685</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>721</v>
+        <v>685</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18000,23 +17911,19 @@
         <v>83</v>
       </c>
       <c r="J128" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>511</v>
+        <v>217</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>722</v>
+        <v>218</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="N128" t="s" s="2">
-        <v>723</v>
-      </c>
-      <c r="O128" t="s" s="2">
-        <v>515</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="N128" s="2"/>
+      <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
         <v>83</v>
       </c>
@@ -18064,7 +17971,7 @@
         <v>83</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>721</v>
+        <v>220</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>81</v>
@@ -18076,44 +17983,44 @@
         <v>83</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK128" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>724</v>
+        <v>83</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>519</v>
+        <v>83</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>520</v>
+        <v>221</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP128" t="s" s="2">
-        <v>521</v>
+        <v>83</v>
       </c>
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>725</v>
+        <v>686</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>725</v>
+        <v>686</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G129" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H129" t="s" s="2">
         <v>83</v>
@@ -18125,20 +18032,18 @@
         <v>83</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>192</v>
+        <v>140</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>726</v>
+        <v>141</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>727</v>
+        <v>223</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>728</v>
-      </c>
-      <c r="O129" t="s" s="2">
-        <v>578</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
         <v>83</v>
       </c>
@@ -18162,13 +18067,13 @@
         <v>83</v>
       </c>
       <c r="X129" t="s" s="2">
-        <v>341</v>
+        <v>83</v>
       </c>
       <c r="Y129" t="s" s="2">
-        <v>579</v>
+        <v>83</v>
       </c>
       <c r="Z129" t="s" s="2">
-        <v>580</v>
+        <v>83</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>83</v>
@@ -18186,19 +18091,19 @@
         <v>83</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>725</v>
+        <v>227</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH129" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI129" t="s" s="2">
-        <v>581</v>
+        <v>83</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK129" t="s" s="2">
         <v>83</v>
@@ -18207,10 +18112,10 @@
         <v>83</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>137</v>
+        <v>83</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>582</v>
+        <v>221</v>
       </c>
       <c r="AO129" t="s" s="2">
         <v>83</v>
@@ -18221,14 +18126,14 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>729</v>
+        <v>687</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>729</v>
+        <v>687</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>584</v>
+        <v>624</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
@@ -18241,25 +18146,25 @@
         <v>83</v>
       </c>
       <c r="I130" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J130" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>192</v>
+        <v>140</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>585</v>
+        <v>625</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>586</v>
+        <v>626</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>587</v>
+        <v>143</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>588</v>
+        <v>149</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>83</v>
@@ -18284,13 +18189,13 @@
         <v>83</v>
       </c>
       <c r="X130" t="s" s="2">
-        <v>341</v>
+        <v>83</v>
       </c>
       <c r="Y130" t="s" s="2">
-        <v>589</v>
+        <v>83</v>
       </c>
       <c r="Z130" t="s" s="2">
-        <v>590</v>
+        <v>83</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>83</v>
@@ -18308,7 +18213,7 @@
         <v>83</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>729</v>
+        <v>627</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>81</v>
@@ -18320,33 +18225,33 @@
         <v>83</v>
       </c>
       <c r="AJ130" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK130" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>591</v>
+        <v>83</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>592</v>
+        <v>83</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>593</v>
+        <v>137</v>
       </c>
       <c r="AO130" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP130" t="s" s="2">
-        <v>594</v>
+        <v>83</v>
       </c>
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>730</v>
+        <v>688</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>730</v>
+        <v>688</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18354,10 +18259,10 @@
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G131" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H131" t="s" s="2">
         <v>83</v>
@@ -18366,22 +18271,22 @@
         <v>83</v>
       </c>
       <c r="J131" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>84</v>
+        <v>192</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>731</v>
+        <v>689</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>732</v>
+        <v>690</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>644</v>
+        <v>691</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>645</v>
+        <v>206</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>83</v>
@@ -18406,13 +18311,13 @@
         <v>83</v>
       </c>
       <c r="X131" t="s" s="2">
-        <v>83</v>
+        <v>207</v>
       </c>
       <c r="Y131" t="s" s="2">
-        <v>83</v>
+        <v>208</v>
       </c>
       <c r="Z131" t="s" s="2">
-        <v>83</v>
+        <v>209</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>83</v>
@@ -18430,13 +18335,13 @@
         <v>83</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>730</v>
+        <v>688</v>
       </c>
       <c r="AG131" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH131" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI131" t="s" s="2">
         <v>83</v>
@@ -18448,23 +18353,511 @@
         <v>83</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>83</v>
+        <v>692</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>647</v>
+        <v>212</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>648</v>
+        <v>213</v>
       </c>
       <c r="AO131" t="s" s="2">
-        <v>83</v>
+        <v>214</v>
       </c>
       <c r="AP131" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="132" hidden="true">
+      <c r="A132" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="B132" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="C132" s="2"/>
+      <c r="D132" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E132" s="2"/>
+      <c r="F132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G132" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H132" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I132" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J132" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K132" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="L132" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="M132" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="N132" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="O132" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="P132" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q132" s="2"/>
+      <c r="R132" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S132" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T132" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U132" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V132" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W132" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X132" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y132" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z132" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA132" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB132" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC132" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD132" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE132" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF132" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="AG132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH132" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI132" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ132" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK132" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL132" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="AM132" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="AN132" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="AO132" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP132" t="s" s="2">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="133" hidden="true">
+      <c r="A133" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="B133" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="C133" s="2"/>
+      <c r="D133" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E133" s="2"/>
+      <c r="F133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G133" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H133" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I133" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J133" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K133" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L133" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="M133" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="N133" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="O133" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="P133" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q133" s="2"/>
+      <c r="R133" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S133" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T133" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U133" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V133" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W133" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X133" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="Y133" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="Z133" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="AA133" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB133" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC133" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD133" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE133" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF133" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="AG133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH133" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI133" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="AJ133" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK133" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL133" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM133" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AN133" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AO133" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP133" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="134" hidden="true">
+      <c r="A134" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="B134" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="C134" s="2"/>
+      <c r="D134" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="E134" s="2"/>
+      <c r="F134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G134" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K134" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L134" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="M134" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="N134" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="O134" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="P134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q134" s="2"/>
+      <c r="R134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X134" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="Y134" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="Z134" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="AA134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF134" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="AG134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH134" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ134" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL134" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="AM134" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="AN134" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="AO134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP134" t="s" s="2">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="135" hidden="true">
+      <c r="A135" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="B135" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="C135" s="2"/>
+      <c r="D135" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E135" s="2"/>
+      <c r="F135" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G135" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H135" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I135" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J135" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K135" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L135" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="M135" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="N135" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="O135" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="P135" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q135" s="2"/>
+      <c r="R135" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S135" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T135" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U135" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V135" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W135" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X135" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y135" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z135" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA135" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB135" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC135" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD135" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE135" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF135" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="AG135" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH135" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI135" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ135" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK135" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL135" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM135" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="AN135" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="AO135" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP135" t="s" s="2">
         <v>83</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP131">
+  <autoFilter ref="A1:AP135">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -18474,7 +18867,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI130">
+  <conditionalFormatting sqref="A2:AI134">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/testbuild/StructureDefinition-vkp-Observation-CFSscore.xlsx
+++ b/testbuild/StructureDefinition-vkp-Observation-CFSscore.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$135</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$131</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5199" uniqueCount="705">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5047" uniqueCount="733">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0-alpha</t>
+    <t>0.5.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-02T06:31:19+00:00</t>
+    <t>2026-10-02T08:56:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1450,7 +1450,7 @@
 </t>
   </si>
   <si>
-    <t>A reference to the author of the observation. Usually an identified Practitioner but can just as likely be an identified role/locations/specialties/services within an organization identified by a PractitionerRole or CareTeam</t>
+    <t>Reference to the author of the observation</t>
   </si>
   <si>
     <t>Reference to the person, role or team that performed the observation, identified by Norwegian national id number (Fødselsnummer or DNR).
@@ -1493,6 +1493,9 @@
     <t>Observation.performer.type</t>
   </si>
   <si>
+    <t>http://hl7.no/fhir/vkpobservation/ValueSet/vkp-performer-reference-types.valueset</t>
+  </si>
+  <si>
     <t>Observation.performer:author.identifier</t>
   </si>
   <si>
@@ -1656,79 +1659,163 @@
     <t>363714003 |Interprets|</t>
   </si>
   <si>
-    <t>Observation.value[x]:valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept.id</t>
+    <t>Observation.value[x]:valueQuantity</t>
+  </si>
+  <si>
+    <t>valueQuantity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity
+</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueQuantity.id</t>
   </si>
   <si>
     <t>Observation.value[x].id</t>
   </si>
   <si>
-    <t>Observation.value[x]:valueCodeableConcept.extension</t>
+    <t>Observation.value[x]:valueQuantity.extension</t>
   </si>
   <si>
     <t>Observation.value[x].extension</t>
   </si>
   <si>
-    <t>Observation.value[x]:valueCodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>Observation.value[x].coding</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept.coding.id</t>
-  </si>
-  <si>
-    <t>Observation.value[x].coding.id</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept.coding.extension</t>
-  </si>
-  <si>
-    <t>Observation.value[x].coding.extension</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept.coding.system</t>
-  </si>
-  <si>
-    <t>Observation.value[x].coding.system</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept.coding.version</t>
-  </si>
-  <si>
-    <t>Observation.value[x].coding.version</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept.coding.code</t>
-  </si>
-  <si>
-    <t>Observation.value[x].coding.code</t>
-  </si>
-  <si>
-    <t>http://hl7.no/fhir/vkpobservation/ValueSet/vkp-cfs-score.valueset</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept.coding.display</t>
-  </si>
-  <si>
-    <t>Observation.value[x].coding.display</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Observation.value[x].coding.userSelected</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept.text</t>
-  </si>
-  <si>
-    <t>Observation.value[x].text</t>
+    <t>Observation.value[x]:valueQuantity.value</t>
+  </si>
+  <si>
+    <t>Observation.value[x].value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">decimal
+</t>
+  </si>
+  <si>
+    <t>Numerical value (with implicit precision)</t>
+  </si>
+  <si>
+    <t>The value of the measured amount. The value includes an implicit precision in the presentation of the value.</t>
+  </si>
+  <si>
+    <t>The implicit precision in the value should always be honored. Monetary values have their own rules for handling precision (refer to standard accounting text books).</t>
+  </si>
+  <si>
+    <t>Precision is handled implicitly in almost all cases of measurement.</t>
+  </si>
+  <si>
+    <t>Quantity.value</t>
+  </si>
+  <si>
+    <t>SN.2  / CQ - N/A</t>
+  </si>
+  <si>
+    <t>PQ.value, CO.value, MO.value, IVL.high or IVL.low depending on the value</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueQuantity.comparator</t>
+  </si>
+  <si>
+    <t>Observation.value[x].comparator</t>
+  </si>
+  <si>
+    <t>&lt; | &lt;= | &gt;= | &gt; - how to understand the value</t>
+  </si>
+  <si>
+    <t>How the value should be understood and represented - whether the actual value is greater or less than the stated value due to measurement issues; e.g. if the comparator is "&lt;" , then the real value is &lt; stated value.</t>
+  </si>
+  <si>
+    <t>Need a framework for handling measures where the value is &lt;5ug/L or &gt;400mg/L due to the limitations of measuring methodology.</t>
+  </si>
+  <si>
+    <t>If there is no comparator, then there is no modification of the value</t>
+  </si>
+  <si>
+    <t>How the Quantity should be understood and represented.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/quantity-comparator|4.0.1</t>
+  </si>
+  <si>
+    <t>Quantity.comparator</t>
+  </si>
+  <si>
+    <t>SN.1  / CQ.1</t>
+  </si>
+  <si>
+    <t>IVL properties</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueQuantity.unit</t>
+  </si>
+  <si>
+    <t>Observation.value[x].unit</t>
+  </si>
+  <si>
+    <t>Unit representation</t>
+  </si>
+  <si>
+    <t>A human-readable form of the unit.</t>
+  </si>
+  <si>
+    <t>There are many representations for units of measure and in many contexts, particular representations are fixed and required. I.e. mcg for micrograms.</t>
+  </si>
+  <si>
+    <t>Quantity.unit</t>
+  </si>
+  <si>
+    <t>(see OBX.6 etc.) / CQ.2</t>
+  </si>
+  <si>
+    <t>PQ.unit</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueQuantity.system</t>
+  </si>
+  <si>
+    <t>Observation.value[x].system</t>
+  </si>
+  <si>
+    <t>System that defines coded unit form</t>
+  </si>
+  <si>
+    <t>The identification of the system that provides the coded form of the unit.</t>
+  </si>
+  <si>
+    <t>Need to know the system that defines the coded form of the unit.</t>
+  </si>
+  <si>
+    <t>Quantity.system</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qty-3
+</t>
+  </si>
+  <si>
+    <t>CO.codeSystem, PQ.translation.codeSystem</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueQuantity.code</t>
+  </si>
+  <si>
+    <t>Observation.value[x].code</t>
+  </si>
+  <si>
+    <t>Coded form of the unit</t>
+  </si>
+  <si>
+    <t>A computer processable form of the unit in some unit representation system.</t>
+  </si>
+  <si>
+    <t>The preferred system is UCUM, but SNOMED CT can also be used (for customary units) or ISO 4217 for currency.  The context of use may additionally require a code from a particular system.</t>
+  </si>
+  <si>
+    <t>Need a computable form of the unit that is fixed across all forms. UCUM provides this for quantities, but SNOMED CT provides many units of interest.</t>
+  </si>
+  <si>
+    <t>Quantity.code</t>
+  </si>
+  <si>
+    <t>PQ.code, MO.currency, PQ.translation.code</t>
   </si>
   <si>
     <t>Observation.dataAbsentReason</t>
@@ -2548,12 +2635,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP135"/>
+  <dimension ref="A1:AP131"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="52.62109375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="44.95703125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="38.30078125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="19.078125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="11.98046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -10853,13 +10940,11 @@
         <v>83</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>342</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="Y69" s="2"/>
       <c r="Z69" t="s" s="2">
-        <v>343</v>
+        <v>468</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>83</v>
@@ -10912,10 +10997,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11032,10 +11117,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11150,10 +11235,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11270,10 +11355,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11392,10 +11477,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11514,10 +11599,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11581,7 +11666,7 @@
       </c>
       <c r="Y75" s="2"/>
       <c r="Z75" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>83</v>
@@ -11634,10 +11719,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11754,10 +11839,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11872,10 +11957,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11992,10 +12077,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12112,13 +12197,13 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>445</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D80" t="s" s="2">
         <v>83</v>
@@ -12140,13 +12225,13 @@
         <v>95</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
@@ -12234,7 +12319,7 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B81" t="s" s="2">
         <v>461</v>
@@ -12352,7 +12437,7 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B82" t="s" s="2">
         <v>463</v>
@@ -12472,7 +12557,7 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B83" t="s" s="2">
         <v>465</v>
@@ -12592,7 +12677,7 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B84" t="s" s="2">
         <v>467</v>
@@ -12712,10 +12797,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12832,10 +12917,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12950,10 +13035,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13070,10 +13155,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13192,10 +13277,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13314,10 +13399,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13381,7 +13466,7 @@
       </c>
       <c r="Y90" s="2"/>
       <c r="Z90" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>83</v>
@@ -13434,10 +13519,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13554,10 +13639,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13672,10 +13757,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13792,10 +13877,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13912,10 +13997,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13938,19 +14023,19 @@
         <v>95</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>83</v>
@@ -13987,7 +14072,7 @@
         <v>83</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AC95" s="2"/>
       <c r="AD95" t="s" s="2">
@@ -13997,7 +14082,7 @@
         <v>226</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -14006,7 +14091,7 @@
         <v>94</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>106</v>
@@ -14015,30 +14100,30 @@
         <v>83</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D96" t="s" s="2">
         <v>83</v>
@@ -14060,19 +14145,19 @@
         <v>95</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>192</v>
+        <v>524</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>83</v>
@@ -14121,7 +14206,7 @@
         <v>83</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -14130,7 +14215,7 @@
         <v>94</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AJ96" t="s" s="2">
         <v>106</v>
@@ -14139,27 +14224,27 @@
         <v>83</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14274,10 +14359,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14392,12 +14477,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="99" hidden="true">
+    <row r="99">
       <c r="A99" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14408,10 +14493,10 @@
         <v>81</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H99" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I99" t="s" s="2">
         <v>83</v>
@@ -14420,19 +14505,19 @@
         <v>95</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>229</v>
+        <v>531</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>230</v>
+        <v>532</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>231</v>
+        <v>533</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>232</v>
+        <v>534</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>233</v>
+        <v>535</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>83</v>
@@ -14481,13 +14566,13 @@
         <v>83</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>236</v>
+        <v>536</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>83</v>
@@ -14502,10 +14587,10 @@
         <v>83</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>237</v>
+        <v>537</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>238</v>
+        <v>538</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>83</v>
@@ -14516,10 +14601,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>529</v>
+        <v>539</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>530</v>
+        <v>540</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14536,26 +14621,30 @@
         <v>83</v>
       </c>
       <c r="I100" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>217</v>
+        <v>114</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>218</v>
+        <v>541</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>219</v>
+        <v>542</v>
       </c>
       <c r="N100" s="2"/>
-      <c r="O100" s="2"/>
+      <c r="O100" t="s" s="2">
+        <v>543</v>
+      </c>
       <c r="P100" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="Q100" s="2"/>
+      <c r="Q100" t="s" s="2">
+        <v>544</v>
+      </c>
       <c r="R100" t="s" s="2">
         <v>83</v>
       </c>
@@ -14575,13 +14664,13 @@
         <v>83</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>83</v>
+        <v>183</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>83</v>
+        <v>545</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>83</v>
+        <v>546</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>83</v>
@@ -14599,7 +14688,7 @@
         <v>83</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>220</v>
+        <v>547</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
@@ -14611,7 +14700,7 @@
         <v>83</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>83</v>
@@ -14620,10 +14709,10 @@
         <v>83</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>83</v>
+        <v>548</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>221</v>
+        <v>549</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>83</v>
@@ -14634,21 +14723,21 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>531</v>
+        <v>550</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>532</v>
+        <v>551</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>83</v>
@@ -14657,21 +14746,21 @@
         <v>83</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>140</v>
+        <v>217</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>141</v>
+        <v>552</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O101" s="2"/>
+        <v>553</v>
+      </c>
+      <c r="N101" s="2"/>
+      <c r="O101" t="s" s="2">
+        <v>554</v>
+      </c>
       <c r="P101" t="s" s="2">
         <v>83</v>
       </c>
@@ -14707,31 +14796,31 @@
         <v>83</v>
       </c>
       <c r="AB101" t="s" s="2">
-        <v>224</v>
+        <v>83</v>
       </c>
       <c r="AC101" t="s" s="2">
-        <v>225</v>
+        <v>83</v>
       </c>
       <c r="AD101" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>226</v>
+        <v>83</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>227</v>
+        <v>555</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>83</v>
@@ -14740,10 +14829,10 @@
         <v>83</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>83</v>
+        <v>556</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>221</v>
+        <v>557</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>83</v>
@@ -14754,10 +14843,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>533</v>
+        <v>558</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>534</v>
+        <v>559</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14783,16 +14872,14 @@
         <v>108</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>247</v>
+        <v>560</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>249</v>
-      </c>
+        <v>561</v>
+      </c>
+      <c r="N102" s="2"/>
       <c r="O102" t="s" s="2">
-        <v>250</v>
+        <v>562</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>83</v>
@@ -14841,7 +14928,7 @@
         <v>83</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>252</v>
+        <v>563</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
@@ -14850,7 +14937,7 @@
         <v>94</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>83</v>
+        <v>564</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>106</v>
@@ -14862,10 +14949,10 @@
         <v>83</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>253</v>
+        <v>556</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>254</v>
+        <v>565</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>83</v>
@@ -14876,10 +14963,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>535</v>
+        <v>566</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>536</v>
+        <v>567</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14902,18 +14989,20 @@
         <v>95</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>217</v>
+        <v>114</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>257</v>
+        <v>568</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>258</v>
+        <v>569</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="O103" s="2"/>
+        <v>570</v>
+      </c>
+      <c r="O103" t="s" s="2">
+        <v>571</v>
+      </c>
       <c r="P103" t="s" s="2">
         <v>83</v>
       </c>
@@ -14961,7 +15050,7 @@
         <v>83</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>260</v>
+        <v>572</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>81</v>
@@ -14982,10 +15071,10 @@
         <v>83</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>261</v>
+        <v>556</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>262</v>
+        <v>573</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>83</v>
@@ -14996,10 +15085,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>537</v>
+        <v>574</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>538</v>
+        <v>574</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15019,20 +15108,22 @@
         <v>83</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>114</v>
+        <v>192</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>265</v>
+        <v>575</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N104" s="2"/>
+        <v>576</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>577</v>
+      </c>
       <c r="O104" t="s" s="2">
-        <v>267</v>
+        <v>578</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>83</v>
@@ -15057,11 +15148,13 @@
         <v>83</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="Y104" s="2"/>
+        <v>341</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>579</v>
+      </c>
       <c r="Z104" t="s" s="2">
-        <v>539</v>
+        <v>580</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>83</v>
@@ -15079,7 +15172,7 @@
         <v>83</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>268</v>
+        <v>574</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>81</v>
@@ -15088,7 +15181,7 @@
         <v>94</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>83</v>
+        <v>581</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>106</v>
@@ -15100,10 +15193,10 @@
         <v>83</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>269</v>
+        <v>137</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>270</v>
+        <v>582</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>83</v>
@@ -15114,21 +15207,21 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>540</v>
+        <v>583</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>541</v>
+        <v>583</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>83</v>
+        <v>584</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>83</v>
@@ -15137,20 +15230,22 @@
         <v>83</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>217</v>
+        <v>192</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>273</v>
+        <v>585</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N105" s="2"/>
+        <v>586</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>587</v>
+      </c>
       <c r="O105" t="s" s="2">
-        <v>275</v>
+        <v>588</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>83</v>
@@ -15175,13 +15270,13 @@
         <v>83</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>83</v>
+        <v>341</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>83</v>
+        <v>589</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>83</v>
+        <v>590</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>83</v>
@@ -15199,13 +15294,13 @@
         <v>83</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>276</v>
+        <v>583</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>83</v>
@@ -15217,27 +15312,27 @@
         <v>83</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>83</v>
+        <v>591</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>277</v>
+        <v>592</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>278</v>
+        <v>593</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP105" t="s" s="2">
-        <v>83</v>
+        <v>594</v>
       </c>
     </row>
-    <row r="106" hidden="true">
+    <row r="106">
       <c r="A106" t="s" s="2">
-        <v>542</v>
+        <v>595</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>543</v>
+        <v>595</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15248,31 +15343,31 @@
         <v>81</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H106" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I106" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>281</v>
+        <v>596</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>282</v>
+        <v>597</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>283</v>
+        <v>598</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>284</v>
+        <v>599</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>285</v>
+        <v>600</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>83</v>
@@ -15321,13 +15416,13 @@
         <v>83</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>286</v>
+        <v>595</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>83</v>
@@ -15342,10 +15437,10 @@
         <v>83</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>287</v>
+        <v>601</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>288</v>
+        <v>602</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>83</v>
@@ -15356,10 +15451,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>544</v>
+        <v>603</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>545</v>
+        <v>603</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15379,23 +15474,21 @@
         <v>83</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>217</v>
+        <v>192</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>312</v>
+        <v>604</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>313</v>
+        <v>605</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>315</v>
-      </c>
+        <v>606</v>
+      </c>
+      <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>83</v>
       </c>
@@ -15419,13 +15512,13 @@
         <v>83</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>83</v>
+        <v>207</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>83</v>
+        <v>607</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>83</v>
+        <v>608</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>83</v>
@@ -15443,7 +15536,7 @@
         <v>83</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>316</v>
+        <v>603</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
@@ -15461,27 +15554,27 @@
         <v>83</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>83</v>
+        <v>609</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>317</v>
+        <v>610</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>318</v>
+        <v>611</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP107" t="s" s="2">
-        <v>83</v>
+        <v>612</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>546</v>
+        <v>613</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>546</v>
+        <v>613</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15507,16 +15600,16 @@
         <v>192</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>547</v>
+        <v>614</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>548</v>
+        <v>615</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>549</v>
+        <v>616</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>550</v>
+        <v>617</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>83</v>
@@ -15541,13 +15634,13 @@
         <v>83</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>341</v>
+        <v>207</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>551</v>
+        <v>618</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>552</v>
+        <v>619</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>83</v>
@@ -15565,7 +15658,7 @@
         <v>83</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>546</v>
+        <v>613</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
@@ -15574,7 +15667,7 @@
         <v>94</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>553</v>
+        <v>83</v>
       </c>
       <c r="AJ108" t="s" s="2">
         <v>106</v>
@@ -15586,10 +15679,10 @@
         <v>83</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>137</v>
+        <v>620</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>554</v>
+        <v>621</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>83</v>
@@ -15600,21 +15693,21 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>555</v>
+        <v>622</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>555</v>
+        <v>622</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>556</v>
+        <v>83</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>83</v>
@@ -15626,20 +15719,18 @@
         <v>83</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>192</v>
+        <v>623</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>557</v>
+        <v>624</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>558</v>
+        <v>625</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="O109" t="s" s="2">
-        <v>560</v>
-      </c>
+        <v>626</v>
+      </c>
+      <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>83</v>
       </c>
@@ -15663,13 +15754,13 @@
         <v>83</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>341</v>
+        <v>83</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>561</v>
+        <v>83</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>562</v>
+        <v>83</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>83</v>
@@ -15687,13 +15778,13 @@
         <v>83</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>555</v>
+        <v>622</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>83</v>
@@ -15705,27 +15796,27 @@
         <v>83</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>563</v>
+        <v>627</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>564</v>
+        <v>628</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>565</v>
+        <v>629</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP109" t="s" s="2">
-        <v>566</v>
+        <v>630</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>567</v>
+        <v>631</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>567</v>
+        <v>631</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15736,10 +15827,10 @@
         <v>81</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H110" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I110" t="s" s="2">
         <v>83</v>
@@ -15748,20 +15839,18 @@
         <v>83</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>568</v>
+        <v>632</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>569</v>
+        <v>633</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>570</v>
+        <v>634</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>572</v>
-      </c>
+        <v>635</v>
+      </c>
+      <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>83</v>
       </c>
@@ -15809,13 +15898,13 @@
         <v>83</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>567</v>
+        <v>631</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>83</v>
@@ -15827,27 +15916,27 @@
         <v>83</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>83</v>
+        <v>636</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>573</v>
+        <v>637</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>574</v>
+        <v>638</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP110" t="s" s="2">
-        <v>83</v>
+        <v>639</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>575</v>
+        <v>640</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>575</v>
+        <v>640</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15858,7 +15947,7 @@
         <v>81</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>83</v>
@@ -15870,18 +15959,20 @@
         <v>83</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>192</v>
+        <v>641</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>576</v>
+        <v>642</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>577</v>
+        <v>643</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="O111" s="2"/>
+        <v>644</v>
+      </c>
+      <c r="O111" t="s" s="2">
+        <v>645</v>
+      </c>
       <c r="P111" t="s" s="2">
         <v>83</v>
       </c>
@@ -15905,13 +15996,13 @@
         <v>83</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>207</v>
+        <v>83</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>579</v>
+        <v>83</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>580</v>
+        <v>83</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>83</v>
@@ -15929,45 +16020,45 @@
         <v>83</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>575</v>
+        <v>640</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>106</v>
+        <v>646</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>581</v>
+        <v>83</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>582</v>
+        <v>647</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>583</v>
+        <v>648</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP111" t="s" s="2">
-        <v>584</v>
+        <v>83</v>
       </c>
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>585</v>
+        <v>649</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>585</v>
+        <v>649</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15990,20 +16081,16 @@
         <v>83</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>586</v>
+        <v>218</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>589</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="N112" s="2"/>
+      <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>83</v>
       </c>
@@ -16027,13 +16114,13 @@
         <v>83</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>207</v>
+        <v>83</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>590</v>
+        <v>83</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>591</v>
+        <v>83</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>83</v>
@@ -16051,7 +16138,7 @@
         <v>83</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>585</v>
+        <v>220</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>81</v>
@@ -16063,7 +16150,7 @@
         <v>83</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK112" t="s" s="2">
         <v>83</v>
@@ -16072,10 +16159,10 @@
         <v>83</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>592</v>
+        <v>83</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>593</v>
+        <v>221</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>83</v>
@@ -16086,21 +16173,21 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>594</v>
+        <v>650</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>594</v>
+        <v>650</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>83</v>
@@ -16112,16 +16199,16 @@
         <v>83</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>595</v>
+        <v>140</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>596</v>
+        <v>141</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>597</v>
+        <v>223</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>598</v>
+        <v>143</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -16171,79 +16258,81 @@
         <v>83</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>594</v>
+        <v>227</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>599</v>
+        <v>83</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>600</v>
+        <v>83</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>601</v>
+        <v>221</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP113" t="s" s="2">
-        <v>602</v>
+        <v>83</v>
       </c>
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>603</v>
+        <v>651</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>603</v>
+        <v>651</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>83</v>
+        <v>652</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I114" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J114" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>604</v>
+        <v>140</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>605</v>
+        <v>653</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>606</v>
+        <v>654</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="O114" s="2"/>
+        <v>143</v>
+      </c>
+      <c r="O114" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P114" t="s" s="2">
         <v>83</v>
       </c>
@@ -16291,45 +16380,45 @@
         <v>83</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>603</v>
+        <v>655</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK114" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>608</v>
+        <v>83</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>609</v>
+        <v>83</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>610</v>
+        <v>137</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP114" t="s" s="2">
-        <v>611</v>
+        <v>83</v>
       </c>
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>612</v>
+        <v>656</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>612</v>
+        <v>656</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16340,7 +16429,7 @@
         <v>81</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>83</v>
@@ -16352,20 +16441,16 @@
         <v>83</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>613</v>
+        <v>657</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>614</v>
+        <v>658</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="O115" t="s" s="2">
-        <v>617</v>
-      </c>
+        <v>659</v>
+      </c>
+      <c r="N115" s="2"/>
+      <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
         <v>83</v>
       </c>
@@ -16413,19 +16498,19 @@
         <v>83</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>612</v>
+        <v>656</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI115" t="s" s="2">
-        <v>83</v>
+        <v>660</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>618</v>
+        <v>106</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>83</v>
@@ -16434,10 +16519,10 @@
         <v>83</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>619</v>
+        <v>661</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>620</v>
+        <v>662</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>83</v>
@@ -16448,10 +16533,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>621</v>
+        <v>663</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>621</v>
+        <v>663</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16474,13 +16559,13 @@
         <v>83</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>217</v>
+        <v>657</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>218</v>
+        <v>664</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>219</v>
+        <v>665</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -16531,7 +16616,7 @@
         <v>83</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>220</v>
+        <v>663</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>81</v>
@@ -16540,10 +16625,10 @@
         <v>94</v>
       </c>
       <c r="AI116" t="s" s="2">
-        <v>83</v>
+        <v>660</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK116" t="s" s="2">
         <v>83</v>
@@ -16552,10 +16637,10 @@
         <v>83</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>83</v>
+        <v>661</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>221</v>
+        <v>666</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>83</v>
@@ -16566,21 +16651,21 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>622</v>
+        <v>667</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>622</v>
+        <v>667</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>83</v>
@@ -16592,18 +16677,20 @@
         <v>83</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>140</v>
+        <v>192</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>141</v>
+        <v>668</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>223</v>
+        <v>669</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O117" s="2"/>
+        <v>670</v>
+      </c>
+      <c r="O117" t="s" s="2">
+        <v>671</v>
+      </c>
       <c r="P117" t="s" s="2">
         <v>83</v>
       </c>
@@ -16627,13 +16714,13 @@
         <v>83</v>
       </c>
       <c r="X117" t="s" s="2">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>83</v>
+        <v>672</v>
       </c>
       <c r="Z117" t="s" s="2">
-        <v>83</v>
+        <v>673</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>83</v>
@@ -16651,31 +16738,31 @@
         <v>83</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>227</v>
+        <v>667</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI117" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>83</v>
+        <v>674</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>83</v>
+        <v>675</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>221</v>
+        <v>593</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>83</v>
@@ -16686,14 +16773,14 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>623</v>
+        <v>676</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>623</v>
+        <v>676</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>624</v>
+        <v>83</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
@@ -16706,25 +16793,25 @@
         <v>83</v>
       </c>
       <c r="I118" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J118" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>140</v>
+        <v>192</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>625</v>
+        <v>677</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>626</v>
+        <v>678</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>143</v>
+        <v>679</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>149</v>
+        <v>680</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>83</v>
@@ -16749,13 +16836,13 @@
         <v>83</v>
       </c>
       <c r="X118" t="s" s="2">
-        <v>83</v>
+        <v>207</v>
       </c>
       <c r="Y118" t="s" s="2">
-        <v>83</v>
+        <v>681</v>
       </c>
       <c r="Z118" t="s" s="2">
-        <v>83</v>
+        <v>682</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>83</v>
@@ -16773,7 +16860,7 @@
         <v>83</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>627</v>
+        <v>676</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>81</v>
@@ -16785,19 +16872,19 @@
         <v>83</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>83</v>
+        <v>674</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>83</v>
+        <v>675</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>137</v>
+        <v>593</v>
       </c>
       <c r="AO118" t="s" s="2">
         <v>83</v>
@@ -16808,10 +16895,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>628</v>
+        <v>683</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>628</v>
+        <v>683</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16834,16 +16921,18 @@
         <v>83</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>629</v>
+        <v>684</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>630</v>
+        <v>685</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>631</v>
+        <v>686</v>
       </c>
       <c r="N119" s="2"/>
-      <c r="O119" s="2"/>
+      <c r="O119" t="s" s="2">
+        <v>687</v>
+      </c>
       <c r="P119" t="s" s="2">
         <v>83</v>
       </c>
@@ -16891,7 +16980,7 @@
         <v>83</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>628</v>
+        <v>683</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>81</v>
@@ -16900,7 +16989,7 @@
         <v>94</v>
       </c>
       <c r="AI119" t="s" s="2">
-        <v>632</v>
+        <v>83</v>
       </c>
       <c r="AJ119" t="s" s="2">
         <v>106</v>
@@ -16912,10 +17001,10 @@
         <v>83</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>633</v>
+        <v>83</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>634</v>
+        <v>688</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>83</v>
@@ -16926,10 +17015,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>635</v>
+        <v>689</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>635</v>
+        <v>689</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16952,13 +17041,13 @@
         <v>83</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>629</v>
+        <v>217</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>636</v>
+        <v>690</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>637</v>
+        <v>691</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -17009,7 +17098,7 @@
         <v>83</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>635</v>
+        <v>689</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>81</v>
@@ -17018,7 +17107,7 @@
         <v>94</v>
       </c>
       <c r="AI120" t="s" s="2">
-        <v>632</v>
+        <v>83</v>
       </c>
       <c r="AJ120" t="s" s="2">
         <v>106</v>
@@ -17030,10 +17119,10 @@
         <v>83</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>633</v>
+        <v>661</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>638</v>
+        <v>692</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>83</v>
@@ -17044,10 +17133,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>639</v>
+        <v>693</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>639</v>
+        <v>693</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17058,7 +17147,7 @@
         <v>81</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H121" t="s" s="2">
         <v>83</v>
@@ -17067,23 +17156,21 @@
         <v>83</v>
       </c>
       <c r="J121" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>192</v>
+        <v>694</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>640</v>
+        <v>695</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>641</v>
+        <v>696</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="O121" t="s" s="2">
-        <v>643</v>
-      </c>
+        <v>697</v>
+      </c>
+      <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
         <v>83</v>
       </c>
@@ -17107,13 +17194,13 @@
         <v>83</v>
       </c>
       <c r="X121" t="s" s="2">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="Y121" t="s" s="2">
-        <v>644</v>
+        <v>83</v>
       </c>
       <c r="Z121" t="s" s="2">
-        <v>645</v>
+        <v>83</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>83</v>
@@ -17131,13 +17218,13 @@
         <v>83</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>639</v>
+        <v>693</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI121" t="s" s="2">
         <v>83</v>
@@ -17149,13 +17236,13 @@
         <v>83</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>646</v>
+        <v>83</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>647</v>
+        <v>698</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>565</v>
+        <v>699</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>83</v>
@@ -17166,10 +17253,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>648</v>
+        <v>700</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>648</v>
+        <v>700</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17189,23 +17276,21 @@
         <v>83</v>
       </c>
       <c r="J122" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>192</v>
+        <v>701</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>649</v>
+        <v>702</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>650</v>
+        <v>703</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="O122" t="s" s="2">
-        <v>652</v>
-      </c>
+        <v>704</v>
+      </c>
+      <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
         <v>83</v>
       </c>
@@ -17229,13 +17314,13 @@
         <v>83</v>
       </c>
       <c r="X122" t="s" s="2">
-        <v>207</v>
+        <v>83</v>
       </c>
       <c r="Y122" t="s" s="2">
-        <v>653</v>
+        <v>83</v>
       </c>
       <c r="Z122" t="s" s="2">
-        <v>654</v>
+        <v>83</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>83</v>
@@ -17253,7 +17338,7 @@
         <v>83</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>648</v>
+        <v>700</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>81</v>
@@ -17271,13 +17356,13 @@
         <v>83</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>646</v>
+        <v>83</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>647</v>
+        <v>698</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>565</v>
+        <v>705</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>83</v>
@@ -17288,10 +17373,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>655</v>
+        <v>706</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>655</v>
+        <v>706</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17302,7 +17387,7 @@
         <v>81</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H123" t="s" s="2">
         <v>83</v>
@@ -17311,20 +17396,22 @@
         <v>83</v>
       </c>
       <c r="J123" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>656</v>
+        <v>641</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>657</v>
+        <v>707</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>658</v>
-      </c>
-      <c r="N123" s="2"/>
+        <v>708</v>
+      </c>
+      <c r="N123" t="s" s="2">
+        <v>709</v>
+      </c>
       <c r="O123" t="s" s="2">
-        <v>659</v>
+        <v>710</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>83</v>
@@ -17373,13 +17460,13 @@
         <v>83</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>655</v>
+        <v>706</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH123" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI123" t="s" s="2">
         <v>83</v>
@@ -17394,10 +17481,10 @@
         <v>83</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>83</v>
+        <v>711</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>660</v>
+        <v>712</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>83</v>
@@ -17408,10 +17495,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>661</v>
+        <v>713</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>661</v>
+        <v>713</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17437,10 +17524,10 @@
         <v>217</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>662</v>
+        <v>218</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>663</v>
+        <v>219</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -17491,7 +17578,7 @@
         <v>83</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>661</v>
+        <v>220</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>81</v>
@@ -17503,7 +17590,7 @@
         <v>83</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK124" t="s" s="2">
         <v>83</v>
@@ -17512,10 +17599,10 @@
         <v>83</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>633</v>
+        <v>83</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>664</v>
+        <v>221</v>
       </c>
       <c r="AO124" t="s" s="2">
         <v>83</v>
@@ -17526,14 +17613,14 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>665</v>
+        <v>714</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>665</v>
+        <v>714</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
@@ -17549,19 +17636,19 @@
         <v>83</v>
       </c>
       <c r="J125" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>666</v>
+        <v>140</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>667</v>
+        <v>141</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>668</v>
+        <v>223</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>669</v>
+        <v>143</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -17611,7 +17698,7 @@
         <v>83</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>665</v>
+        <v>227</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>81</v>
@@ -17623,7 +17710,7 @@
         <v>83</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK125" t="s" s="2">
         <v>83</v>
@@ -17632,10 +17719,10 @@
         <v>83</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>670</v>
+        <v>83</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>671</v>
+        <v>221</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>83</v>
@@ -17646,14 +17733,14 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>672</v>
+        <v>715</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>672</v>
+        <v>715</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
-        <v>83</v>
+        <v>652</v>
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
@@ -17666,24 +17753,26 @@
         <v>83</v>
       </c>
       <c r="I126" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J126" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>673</v>
+        <v>140</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>674</v>
+        <v>653</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>675</v>
+        <v>654</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>676</v>
-      </c>
-      <c r="O126" s="2"/>
+        <v>143</v>
+      </c>
+      <c r="O126" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P126" t="s" s="2">
         <v>83</v>
       </c>
@@ -17731,7 +17820,7 @@
         <v>83</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>672</v>
+        <v>655</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>81</v>
@@ -17743,7 +17832,7 @@
         <v>83</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK126" t="s" s="2">
         <v>83</v>
@@ -17752,10 +17841,10 @@
         <v>83</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>670</v>
+        <v>83</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>677</v>
+        <v>137</v>
       </c>
       <c r="AO126" t="s" s="2">
         <v>83</v>
@@ -17766,10 +17855,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>678</v>
+        <v>716</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>678</v>
+        <v>716</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17777,10 +17866,10 @@
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G127" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H127" t="s" s="2">
         <v>83</v>
@@ -17792,19 +17881,19 @@
         <v>95</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>613</v>
+        <v>192</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>679</v>
+        <v>717</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>680</v>
+        <v>718</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>681</v>
+        <v>719</v>
       </c>
       <c r="O127" t="s" s="2">
-        <v>682</v>
+        <v>206</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>83</v>
@@ -17829,13 +17918,13 @@
         <v>83</v>
       </c>
       <c r="X127" t="s" s="2">
-        <v>83</v>
+        <v>207</v>
       </c>
       <c r="Y127" t="s" s="2">
-        <v>83</v>
+        <v>208</v>
       </c>
       <c r="Z127" t="s" s="2">
-        <v>83</v>
+        <v>209</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>83</v>
@@ -17853,13 +17942,13 @@
         <v>83</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>678</v>
+        <v>716</v>
       </c>
       <c r="AG127" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH127" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI127" t="s" s="2">
         <v>83</v>
@@ -17871,16 +17960,16 @@
         <v>83</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>83</v>
+        <v>720</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>683</v>
+        <v>212</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>684</v>
+        <v>213</v>
       </c>
       <c r="AO127" t="s" s="2">
-        <v>83</v>
+        <v>214</v>
       </c>
       <c r="AP127" t="s" s="2">
         <v>83</v>
@@ -17888,10 +17977,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>685</v>
+        <v>721</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>685</v>
+        <v>721</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17911,19 +18000,23 @@
         <v>83</v>
       </c>
       <c r="J128" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>217</v>
+        <v>511</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>218</v>
+        <v>722</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N128" s="2"/>
-      <c r="O128" s="2"/>
+        <v>513</v>
+      </c>
+      <c r="N128" t="s" s="2">
+        <v>723</v>
+      </c>
+      <c r="O128" t="s" s="2">
+        <v>515</v>
+      </c>
       <c r="P128" t="s" s="2">
         <v>83</v>
       </c>
@@ -17971,7 +18064,7 @@
         <v>83</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>220</v>
+        <v>721</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>81</v>
@@ -17983,44 +18076,44 @@
         <v>83</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK128" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>83</v>
+        <v>724</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>83</v>
+        <v>519</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>221</v>
+        <v>520</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP128" t="s" s="2">
-        <v>83</v>
+        <v>521</v>
       </c>
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>686</v>
+        <v>725</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>686</v>
+        <v>725</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G129" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H129" t="s" s="2">
         <v>83</v>
@@ -18032,18 +18125,20 @@
         <v>83</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>140</v>
+        <v>192</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>141</v>
+        <v>726</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>223</v>
+        <v>727</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O129" s="2"/>
+        <v>728</v>
+      </c>
+      <c r="O129" t="s" s="2">
+        <v>578</v>
+      </c>
       <c r="P129" t="s" s="2">
         <v>83</v>
       </c>
@@ -18067,13 +18162,13 @@
         <v>83</v>
       </c>
       <c r="X129" t="s" s="2">
-        <v>83</v>
+        <v>341</v>
       </c>
       <c r="Y129" t="s" s="2">
-        <v>83</v>
+        <v>579</v>
       </c>
       <c r="Z129" t="s" s="2">
-        <v>83</v>
+        <v>580</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>83</v>
@@ -18091,19 +18186,19 @@
         <v>83</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>227</v>
+        <v>725</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH129" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI129" t="s" s="2">
-        <v>83</v>
+        <v>581</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK129" t="s" s="2">
         <v>83</v>
@@ -18112,10 +18207,10 @@
         <v>83</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>83</v>
+        <v>137</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>221</v>
+        <v>582</v>
       </c>
       <c r="AO129" t="s" s="2">
         <v>83</v>
@@ -18126,14 +18221,14 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>687</v>
+        <v>729</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>687</v>
+        <v>729</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>624</v>
+        <v>584</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
@@ -18146,25 +18241,25 @@
         <v>83</v>
       </c>
       <c r="I130" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J130" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>140</v>
+        <v>192</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>625</v>
+        <v>585</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>626</v>
+        <v>586</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>143</v>
+        <v>587</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>149</v>
+        <v>588</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>83</v>
@@ -18189,13 +18284,13 @@
         <v>83</v>
       </c>
       <c r="X130" t="s" s="2">
-        <v>83</v>
+        <v>341</v>
       </c>
       <c r="Y130" t="s" s="2">
-        <v>83</v>
+        <v>589</v>
       </c>
       <c r="Z130" t="s" s="2">
-        <v>83</v>
+        <v>590</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>83</v>
@@ -18213,7 +18308,7 @@
         <v>83</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>627</v>
+        <v>729</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>81</v>
@@ -18225,33 +18320,33 @@
         <v>83</v>
       </c>
       <c r="AJ130" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK130" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>83</v>
+        <v>591</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>83</v>
+        <v>592</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>137</v>
+        <v>593</v>
       </c>
       <c r="AO130" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP130" t="s" s="2">
-        <v>83</v>
+        <v>594</v>
       </c>
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>688</v>
+        <v>730</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>688</v>
+        <v>730</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18259,10 +18354,10 @@
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G131" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H131" t="s" s="2">
         <v>83</v>
@@ -18271,22 +18366,22 @@
         <v>83</v>
       </c>
       <c r="J131" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>192</v>
+        <v>84</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>689</v>
+        <v>731</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>690</v>
+        <v>732</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>691</v>
+        <v>644</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>206</v>
+        <v>645</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>83</v>
@@ -18311,13 +18406,13 @@
         <v>83</v>
       </c>
       <c r="X131" t="s" s="2">
-        <v>207</v>
+        <v>83</v>
       </c>
       <c r="Y131" t="s" s="2">
-        <v>208</v>
+        <v>83</v>
       </c>
       <c r="Z131" t="s" s="2">
-        <v>209</v>
+        <v>83</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>83</v>
@@ -18335,13 +18430,13 @@
         <v>83</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>688</v>
+        <v>730</v>
       </c>
       <c r="AG131" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH131" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI131" t="s" s="2">
         <v>83</v>
@@ -18353,511 +18448,23 @@
         <v>83</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>692</v>
+        <v>83</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>212</v>
+        <v>647</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>213</v>
+        <v>648</v>
       </c>
       <c r="AO131" t="s" s="2">
-        <v>214</v>
+        <v>83</v>
       </c>
       <c r="AP131" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="132" hidden="true">
-      <c r="A132" t="s" s="2">
-        <v>693</v>
-      </c>
-      <c r="B132" t="s" s="2">
-        <v>693</v>
-      </c>
-      <c r="C132" s="2"/>
-      <c r="D132" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E132" s="2"/>
-      <c r="F132" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G132" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H132" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I132" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J132" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K132" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="L132" t="s" s="2">
-        <v>694</v>
-      </c>
-      <c r="M132" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>695</v>
-      </c>
-      <c r="O132" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="P132" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q132" s="2"/>
-      <c r="R132" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S132" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T132" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U132" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V132" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W132" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X132" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y132" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z132" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA132" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB132" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC132" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD132" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE132" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF132" t="s" s="2">
-        <v>693</v>
-      </c>
-      <c r="AG132" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH132" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI132" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ132" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK132" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL132" t="s" s="2">
-        <v>696</v>
-      </c>
-      <c r="AM132" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="AN132" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="AO132" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP132" t="s" s="2">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="133" hidden="true">
-      <c r="A133" t="s" s="2">
-        <v>697</v>
-      </c>
-      <c r="B133" t="s" s="2">
-        <v>697</v>
-      </c>
-      <c r="C133" s="2"/>
-      <c r="D133" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E133" s="2"/>
-      <c r="F133" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G133" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H133" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I133" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J133" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K133" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="L133" t="s" s="2">
-        <v>698</v>
-      </c>
-      <c r="M133" t="s" s="2">
-        <v>699</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>700</v>
-      </c>
-      <c r="O133" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="P133" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q133" s="2"/>
-      <c r="R133" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S133" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T133" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U133" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V133" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W133" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X133" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="Y133" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="Z133" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="AA133" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB133" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC133" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD133" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE133" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF133" t="s" s="2">
-        <v>697</v>
-      </c>
-      <c r="AG133" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH133" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI133" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="AJ133" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK133" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL133" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM133" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AN133" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="AO133" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP133" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="134" hidden="true">
-      <c r="A134" t="s" s="2">
-        <v>701</v>
-      </c>
-      <c r="B134" t="s" s="2">
-        <v>701</v>
-      </c>
-      <c r="C134" s="2"/>
-      <c r="D134" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="E134" s="2"/>
-      <c r="F134" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G134" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H134" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I134" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J134" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K134" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="L134" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="M134" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="N134" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="O134" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="P134" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q134" s="2"/>
-      <c r="R134" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S134" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T134" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U134" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V134" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W134" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X134" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="Y134" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="Z134" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="AA134" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB134" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC134" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD134" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE134" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF134" t="s" s="2">
-        <v>701</v>
-      </c>
-      <c r="AG134" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH134" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI134" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ134" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK134" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL134" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="AM134" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="AN134" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="AO134" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP134" t="s" s="2">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="135" hidden="true">
-      <c r="A135" t="s" s="2">
-        <v>702</v>
-      </c>
-      <c r="B135" t="s" s="2">
-        <v>702</v>
-      </c>
-      <c r="C135" s="2"/>
-      <c r="D135" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E135" s="2"/>
-      <c r="F135" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G135" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H135" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I135" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J135" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K135" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="L135" t="s" s="2">
-        <v>703</v>
-      </c>
-      <c r="M135" t="s" s="2">
-        <v>704</v>
-      </c>
-      <c r="N135" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="O135" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="P135" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q135" s="2"/>
-      <c r="R135" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S135" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T135" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U135" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V135" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W135" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X135" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y135" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z135" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA135" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB135" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC135" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD135" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE135" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF135" t="s" s="2">
-        <v>702</v>
-      </c>
-      <c r="AG135" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH135" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI135" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ135" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK135" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL135" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM135" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="AN135" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="AO135" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP135" t="s" s="2">
         <v>83</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP135">
+  <autoFilter ref="A1:AP131">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -18867,7 +18474,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI134">
+  <conditionalFormatting sqref="A2:AI130">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/testbuild/StructureDefinition-vkp-Observation-CFSscore.xlsx
+++ b/testbuild/StructureDefinition-vkp-Observation-CFSscore.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$131</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$134</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5047" uniqueCount="733">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5160" uniqueCount="691">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.2</t>
+    <t>0.6.0-alpha</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-02T08:56:17+00:00</t>
+    <t>2026-10-02T09:03:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1440,20 +1440,20 @@
     <t>FiveWs.actor</t>
   </si>
   <si>
-    <t>Observation.performer:author</t>
-  </si>
-  <si>
-    <t>author</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|CareTeam|Patient|RelatedPerson|http://hl7.no/fhir/StructureDefinition/no-basis-Practitioner|http://hl7.no/fhir/StructureDefinition/no-basis-PractitionerRole)
+    <t>Observation.performer:authorperson</t>
+  </si>
+  <si>
+    <t>authorperson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Practitioner|http://hl7.no/fhir/StructureDefinition/no-basis-Practitioner|Patient|RelatedPerson)
 </t>
   </si>
   <si>
-    <t>Reference to the author of the observation</t>
-  </si>
-  <si>
-    <t>Reference to the person, role or team that performed the observation, identified by Norwegian national id number (Fødselsnummer or DNR).
+    <t>When the perfomer is an identified person, otherwise use CareTeam, PractitionerRole etc.</t>
+  </si>
+  <si>
+    <t>Reference to the person that performed the observation, identified by Norwegian national id number (Fødselsnummer).
 A link to a resource representing the person or the group to whom the medication will be given.
 VKP always references a Practitioner Resource using a norwegian national id number (Fødselsnummer or DNR) in a logical identifier in the practitioner.identifier element.
 The Name of the practitioner should be given in the performer.display element.
@@ -1469,64 +1469,61 @@
 ~~~~</t>
   </si>
   <si>
-    <t>Observation.performer:author.id</t>
+    <t>Observation.performer:authorperson.id</t>
   </si>
   <si>
     <t>Observation.performer.id</t>
   </si>
   <si>
-    <t>Observation.performer:author.extension</t>
+    <t>Observation.performer:authorperson.extension</t>
   </si>
   <si>
     <t>Observation.performer.extension</t>
   </si>
   <si>
-    <t>Observation.performer:author.reference</t>
+    <t>Observation.performer:authorperson.reference</t>
   </si>
   <si>
     <t>Observation.performer.reference</t>
   </si>
   <si>
-    <t>Observation.performer:author.type</t>
+    <t>Observation.performer:authorperson.type</t>
   </si>
   <si>
     <t>Observation.performer.type</t>
   </si>
   <si>
-    <t>http://hl7.no/fhir/vkpobservation/ValueSet/vkp-performer-reference-types.valueset</t>
-  </si>
-  <si>
-    <t>Observation.performer:author.identifier</t>
+    <t>Observation.performer:authorperson.identifier</t>
   </si>
   <si>
     <t>Observation.performer.identifier</t>
   </si>
   <si>
-    <t>Observation.performer:author.identifier.id</t>
+    <t>Observation.performer:authorperson.identifier.id</t>
   </si>
   <si>
     <t>Observation.performer.identifier.id</t>
   </si>
   <si>
-    <t>Observation.performer:author.identifier.extension</t>
+    <t>Observation.performer:authorperson.identifier.extension</t>
   </si>
   <si>
     <t>Observation.performer.identifier.extension</t>
   </si>
   <si>
-    <t>Observation.performer:author.identifier.use</t>
+    <t>Observation.performer:authorperson.identifier.use</t>
   </si>
   <si>
     <t>Observation.performer.identifier.use</t>
   </si>
   <si>
-    <t>Observation.performer:author.identifier.type</t>
+    <t>Observation.performer:authorperson.identifier.type</t>
   </si>
   <si>
     <t>Observation.performer.identifier.type</t>
   </si>
   <si>
-    <t>Observation.performer:author.identifier.system</t>
+    <t>Observation.performer:authorperson.identifier.system</t>
   </si>
   <si>
     <t>Observation.performer.identifier.system</t>
@@ -1535,25 +1532,25 @@
     <t>http://hl7.no/fhir/vkpobservation/ValueSet/vkp-performer-identifiers.valueset</t>
   </si>
   <si>
-    <t>Observation.performer:author.identifier.value</t>
+    <t>Observation.performer:authorperson.identifier.value</t>
   </si>
   <si>
     <t>Observation.performer.identifier.value</t>
   </si>
   <si>
-    <t>Observation.performer:author.identifier.period</t>
+    <t>Observation.performer:authorperson.identifier.period</t>
   </si>
   <si>
     <t>Observation.performer.identifier.period</t>
   </si>
   <si>
-    <t>Observation.performer:author.identifier.assigner</t>
+    <t>Observation.performer:authorperson.identifier.assigner</t>
   </si>
   <si>
     <t>Observation.performer.identifier.assigner</t>
   </si>
   <si>
-    <t>Observation.performer:author.display</t>
+    <t>Observation.performer:authorperson.display</t>
   </si>
   <si>
     <t>Observation.performer.display</t>
@@ -1623,10 +1620,6 @@
     <t>Observation.value[x]</t>
   </si>
   <si>
-    <t>Quantity
-CodeableConceptstringbooleanintegerRangeRatioSampledDatatimedateTimePeriod</t>
-  </si>
-  <si>
     <t>Actual result</t>
   </si>
   <si>
@@ -1637,10 +1630,6 @@
   </si>
   <si>
     <t>An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type:$this}
-</t>
   </si>
   <si>
     <t xml:space="preserve">obs-7
@@ -1659,163 +1648,40 @@
     <t>363714003 |Interprets|</t>
   </si>
   <si>
-    <t>Observation.value[x]:valueQuantity</t>
-  </si>
-  <si>
-    <t>valueQuantity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantity
-</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueQuantity.id</t>
-  </si>
-  <si>
     <t>Observation.value[x].id</t>
   </si>
   <si>
-    <t>Observation.value[x]:valueQuantity.extension</t>
-  </si>
-  <si>
     <t>Observation.value[x].extension</t>
   </si>
   <si>
-    <t>Observation.value[x]:valueQuantity.value</t>
-  </si>
-  <si>
-    <t>Observation.value[x].value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">decimal
-</t>
-  </si>
-  <si>
-    <t>Numerical value (with implicit precision)</t>
-  </si>
-  <si>
-    <t>The value of the measured amount. The value includes an implicit precision in the presentation of the value.</t>
-  </si>
-  <si>
-    <t>The implicit precision in the value should always be honored. Monetary values have their own rules for handling precision (refer to standard accounting text books).</t>
-  </si>
-  <si>
-    <t>Precision is handled implicitly in almost all cases of measurement.</t>
-  </si>
-  <si>
-    <t>Quantity.value</t>
-  </si>
-  <si>
-    <t>SN.2  / CQ - N/A</t>
-  </si>
-  <si>
-    <t>PQ.value, CO.value, MO.value, IVL.high or IVL.low depending on the value</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueQuantity.comparator</t>
-  </si>
-  <si>
-    <t>Observation.value[x].comparator</t>
-  </si>
-  <si>
-    <t>&lt; | &lt;= | &gt;= | &gt; - how to understand the value</t>
-  </si>
-  <si>
-    <t>How the value should be understood and represented - whether the actual value is greater or less than the stated value due to measurement issues; e.g. if the comparator is "&lt;" , then the real value is &lt; stated value.</t>
-  </si>
-  <si>
-    <t>Need a framework for handling measures where the value is &lt;5ug/L or &gt;400mg/L due to the limitations of measuring methodology.</t>
-  </si>
-  <si>
-    <t>If there is no comparator, then there is no modification of the value</t>
-  </si>
-  <si>
-    <t>How the Quantity should be understood and represented.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/quantity-comparator|4.0.1</t>
-  </si>
-  <si>
-    <t>Quantity.comparator</t>
-  </si>
-  <si>
-    <t>SN.1  / CQ.1</t>
-  </si>
-  <si>
-    <t>IVL properties</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueQuantity.unit</t>
-  </si>
-  <si>
-    <t>Observation.value[x].unit</t>
-  </si>
-  <si>
-    <t>Unit representation</t>
-  </si>
-  <si>
-    <t>A human-readable form of the unit.</t>
-  </si>
-  <si>
-    <t>There are many representations for units of measure and in many contexts, particular representations are fixed and required. I.e. mcg for micrograms.</t>
-  </si>
-  <si>
-    <t>Quantity.unit</t>
-  </si>
-  <si>
-    <t>(see OBX.6 etc.) / CQ.2</t>
-  </si>
-  <si>
-    <t>PQ.unit</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueQuantity.system</t>
-  </si>
-  <si>
-    <t>Observation.value[x].system</t>
-  </si>
-  <si>
-    <t>System that defines coded unit form</t>
-  </si>
-  <si>
-    <t>The identification of the system that provides the coded form of the unit.</t>
-  </si>
-  <si>
-    <t>Need to know the system that defines the coded form of the unit.</t>
-  </si>
-  <si>
-    <t>Quantity.system</t>
-  </si>
-  <si>
-    <t xml:space="preserve">qty-3
-</t>
-  </si>
-  <si>
-    <t>CO.codeSystem, PQ.translation.codeSystem</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueQuantity.code</t>
-  </si>
-  <si>
-    <t>Observation.value[x].code</t>
-  </si>
-  <si>
-    <t>Coded form of the unit</t>
-  </si>
-  <si>
-    <t>A computer processable form of the unit in some unit representation system.</t>
-  </si>
-  <si>
-    <t>The preferred system is UCUM, but SNOMED CT can also be used (for customary units) or ISO 4217 for currency.  The context of use may additionally require a code from a particular system.</t>
-  </si>
-  <si>
-    <t>Need a computable form of the unit that is fixed across all forms. UCUM provides this for quantities, but SNOMED CT provides many units of interest.</t>
-  </si>
-  <si>
-    <t>Quantity.code</t>
-  </si>
-  <si>
-    <t>PQ.code, MO.currency, PQ.translation.code</t>
+    <t>Observation.value[x].coding</t>
+  </si>
+  <si>
+    <t>Observation.value[x].coding.id</t>
+  </si>
+  <si>
+    <t>Observation.value[x].coding.extension</t>
+  </si>
+  <si>
+    <t>Observation.value[x].coding.system</t>
+  </si>
+  <si>
+    <t>Observation.value[x].coding.version</t>
+  </si>
+  <si>
+    <t>Observation.value[x].coding.code</t>
+  </si>
+  <si>
+    <t>http://hl7.no/fhir/vkpobservation/ValueSet/vkp-cfs-score.valueset</t>
+  </si>
+  <si>
+    <t>Observation.value[x].coding.display</t>
+  </si>
+  <si>
+    <t>Observation.value[x].coding.userSelected</t>
+  </si>
+  <si>
+    <t>Observation.value[x].text</t>
   </si>
   <si>
     <t>Observation.dataAbsentReason</t>
@@ -2283,6 +2149,10 @@
   </si>
   <si>
     <t>Observation.component.value[x]</t>
+  </si>
+  <si>
+    <t>Quantity
+CodeableConceptstringbooleanintegerRangeRatioSampledDatatimedateTimePeriod</t>
   </si>
   <si>
     <t>Actual component result</t>
@@ -2635,12 +2505,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP131"/>
+  <dimension ref="A1:AP134"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="44.95703125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="45.72265625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="38.30078125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.98046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="11.4609375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -2648,7 +2518,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="153.6640625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="122.43359375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -10877,7 +10747,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
         <v>466</v>
       </c>
@@ -10896,7 +10766,7 @@
         <v>94</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>83</v>
@@ -10940,11 +10810,13 @@
         <v>83</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="Y69" s="2"/>
+        <v>341</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>342</v>
+      </c>
       <c r="Z69" t="s" s="2">
-        <v>468</v>
+        <v>343</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>83</v>
@@ -10997,10 +10869,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B70" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>470</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11117,10 +10989,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="B71" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>472</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11235,10 +11107,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="B72" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11355,10 +11227,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="B73" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>476</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11477,10 +11349,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="B74" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11599,10 +11471,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="B75" t="s" s="2">
         <v>479</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>480</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11666,7 +11538,7 @@
       </c>
       <c r="Y75" s="2"/>
       <c r="Z75" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>83</v>
@@ -11719,10 +11591,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="B76" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>483</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11839,10 +11711,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="B77" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>485</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11957,10 +11829,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="B78" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="B78" t="s" s="2">
-        <v>487</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12077,10 +11949,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="B79" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>489</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12197,13 +12069,13 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>445</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D80" t="s" s="2">
         <v>83</v>
@@ -12225,13 +12097,13 @@
         <v>95</v>
       </c>
       <c r="K80" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="L80" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="L80" t="s" s="2">
+      <c r="M80" t="s" s="2">
         <v>493</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>494</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
@@ -12319,7 +12191,7 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B81" t="s" s="2">
         <v>461</v>
@@ -12437,7 +12309,7 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B82" t="s" s="2">
         <v>463</v>
@@ -12557,7 +12429,7 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B83" t="s" s="2">
         <v>465</v>
@@ -12677,7 +12549,7 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B84" t="s" s="2">
         <v>467</v>
@@ -12797,10 +12669,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12917,10 +12789,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13035,10 +12907,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13155,10 +13027,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13277,10 +13149,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13399,10 +13271,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13466,7 +13338,7 @@
       </c>
       <c r="Y90" s="2"/>
       <c r="Z90" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>83</v>
@@ -13519,10 +13391,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13639,10 +13511,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13757,10 +13629,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13877,10 +13749,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13995,12 +13867,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="95" hidden="true">
+    <row r="95">
       <c r="A95" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14014,7 +13886,7 @@
         <v>94</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>83</v>
@@ -14023,19 +13895,19 @@
         <v>95</v>
       </c>
       <c r="K95" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L95" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="L95" t="s" s="2">
+      <c r="N95" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="M95" t="s" s="2">
+      <c r="O95" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>515</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>83</v>
@@ -14072,17 +13944,19 @@
         <v>83</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="AC95" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="AD95" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>226</v>
+        <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -14091,7 +13965,7 @@
         <v>94</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>106</v>
@@ -14100,31 +13974,29 @@
         <v>83</v>
       </c>
       <c r="AL95" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="AN95" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="AO95" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP95" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="AM95" t="s" s="2">
+    </row>
+    <row r="96" hidden="true">
+      <c r="A96" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="AN95" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="AO95" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP95" t="s" s="2">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="s" s="2">
-        <v>522</v>
-      </c>
       <c r="B96" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="C96" t="s" s="2">
-        <v>523</v>
-      </c>
+        <v>519</v>
+      </c>
+      <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
         <v>83</v>
       </c>
@@ -14136,29 +14008,25 @@
         <v>94</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I96" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>524</v>
+        <v>217</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>512</v>
+        <v>218</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>515</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="N96" s="2"/>
+      <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>83</v>
       </c>
@@ -14206,7 +14074,7 @@
         <v>83</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>510</v>
+        <v>220</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -14215,47 +14083,47 @@
         <v>94</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>517</v>
+        <v>83</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>518</v>
+        <v>83</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>519</v>
+        <v>83</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>520</v>
+        <v>221</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>521</v>
+        <v>83</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>83</v>
@@ -14267,15 +14135,17 @@
         <v>83</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>217</v>
+        <v>140</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>218</v>
+        <v>141</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N97" s="2"/>
+        <v>223</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>83</v>
@@ -14312,31 +14182,31 @@
         <v>83</v>
       </c>
       <c r="AB97" t="s" s="2">
-        <v>83</v>
+        <v>224</v>
       </c>
       <c r="AC97" t="s" s="2">
-        <v>83</v>
+        <v>225</v>
       </c>
       <c r="AD97" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>83</v>
+        <v>226</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>83</v>
@@ -14359,14 +14229,14 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
@@ -14382,21 +14252,23 @@
         <v>83</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>140</v>
+        <v>229</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>141</v>
+        <v>230</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O98" s="2"/>
+        <v>232</v>
+      </c>
+      <c r="O98" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="P98" t="s" s="2">
         <v>83</v>
       </c>
@@ -14432,19 +14304,19 @@
         <v>83</v>
       </c>
       <c r="AB98" t="s" s="2">
-        <v>224</v>
+        <v>83</v>
       </c>
       <c r="AC98" t="s" s="2">
-        <v>225</v>
+        <v>83</v>
       </c>
       <c r="AD98" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE98" t="s" s="2">
-        <v>226</v>
+        <v>83</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -14456,7 +14328,7 @@
         <v>83</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>83</v>
@@ -14465,10 +14337,10 @@
         <v>83</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>83</v>
+        <v>237</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>83</v>
@@ -14477,12 +14349,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14496,29 +14368,25 @@
         <v>94</v>
       </c>
       <c r="H99" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I99" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>531</v>
+        <v>217</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>532</v>
+        <v>218</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>535</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="N99" s="2"/>
+      <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>83</v>
       </c>
@@ -14566,7 +14434,7 @@
         <v>83</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>536</v>
+        <v>220</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -14578,7 +14446,7 @@
         <v>83</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>83</v>
@@ -14587,10 +14455,10 @@
         <v>83</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>537</v>
+        <v>83</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>538</v>
+        <v>221</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>83</v>
@@ -14601,50 +14469,48 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>539</v>
+        <v>523</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>540</v>
+        <v>523</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I100" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>541</v>
+        <v>141</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="N100" s="2"/>
-      <c r="O100" t="s" s="2">
-        <v>543</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="Q100" t="s" s="2">
-        <v>544</v>
-      </c>
+      <c r="Q100" s="2"/>
       <c r="R100" t="s" s="2">
         <v>83</v>
       </c>
@@ -14664,43 +14530,43 @@
         <v>83</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>183</v>
+        <v>83</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>545</v>
+        <v>83</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>546</v>
+        <v>83</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB100" t="s" s="2">
-        <v>83</v>
+        <v>224</v>
       </c>
       <c r="AC100" t="s" s="2">
-        <v>83</v>
+        <v>225</v>
       </c>
       <c r="AD100" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE100" t="s" s="2">
-        <v>83</v>
+        <v>226</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>547</v>
+        <v>227</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>83</v>
@@ -14709,10 +14575,10 @@
         <v>83</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>548</v>
+        <v>83</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>549</v>
+        <v>221</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>83</v>
@@ -14723,10 +14589,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>550</v>
+        <v>524</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>551</v>
+        <v>524</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14749,17 +14615,19 @@
         <v>95</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>217</v>
+        <v>108</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>552</v>
+        <v>247</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="N101" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>249</v>
+      </c>
       <c r="O101" t="s" s="2">
-        <v>554</v>
+        <v>250</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>83</v>
@@ -14808,7 +14676,7 @@
         <v>83</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>555</v>
+        <v>252</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
@@ -14829,10 +14697,10 @@
         <v>83</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>556</v>
+        <v>253</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>557</v>
+        <v>254</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>83</v>
@@ -14843,10 +14711,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>558</v>
+        <v>525</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>559</v>
+        <v>525</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14869,18 +14737,18 @@
         <v>95</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>108</v>
+        <v>217</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>560</v>
+        <v>257</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="N102" s="2"/>
-      <c r="O102" t="s" s="2">
-        <v>562</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>83</v>
       </c>
@@ -14928,7 +14796,7 @@
         <v>83</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>563</v>
+        <v>260</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
@@ -14937,7 +14805,7 @@
         <v>94</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>564</v>
+        <v>83</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>106</v>
@@ -14949,10 +14817,10 @@
         <v>83</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>556</v>
+        <v>261</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>565</v>
+        <v>262</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>83</v>
@@ -14963,10 +14831,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>566</v>
+        <v>526</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>567</v>
+        <v>526</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14992,16 +14860,14 @@
         <v>114</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>568</v>
+        <v>265</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>570</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="N103" s="2"/>
       <c r="O103" t="s" s="2">
-        <v>571</v>
+        <v>267</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>83</v>
@@ -15026,13 +14892,11 @@
         <v>83</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y103" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="Y103" s="2"/>
       <c r="Z103" t="s" s="2">
-        <v>83</v>
+        <v>527</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>83</v>
@@ -15050,7 +14914,7 @@
         <v>83</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>572</v>
+        <v>268</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>81</v>
@@ -15071,10 +14935,10 @@
         <v>83</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>556</v>
+        <v>269</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>573</v>
+        <v>270</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>83</v>
@@ -15085,10 +14949,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>574</v>
+        <v>528</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>574</v>
+        <v>528</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15108,22 +14972,20 @@
         <v>83</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>575</v>
+        <v>273</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>577</v>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="N104" s="2"/>
       <c r="O104" t="s" s="2">
-        <v>578</v>
+        <v>275</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>83</v>
@@ -15148,13 +15010,13 @@
         <v>83</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>341</v>
+        <v>83</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>579</v>
+        <v>83</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>580</v>
+        <v>83</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>83</v>
@@ -15172,7 +15034,7 @@
         <v>83</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>574</v>
+        <v>276</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>81</v>
@@ -15181,7 +15043,7 @@
         <v>94</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>581</v>
+        <v>83</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>106</v>
@@ -15193,10 +15055,10 @@
         <v>83</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>137</v>
+        <v>277</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>582</v>
+        <v>278</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>83</v>
@@ -15207,21 +15069,21 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>583</v>
+        <v>529</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>583</v>
+        <v>529</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>584</v>
+        <v>83</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>83</v>
@@ -15230,22 +15092,22 @@
         <v>83</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>192</v>
+        <v>281</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>585</v>
+        <v>282</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>586</v>
+        <v>283</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>587</v>
+        <v>284</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>588</v>
+        <v>285</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>83</v>
@@ -15270,13 +15132,13 @@
         <v>83</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>341</v>
+        <v>83</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>589</v>
+        <v>83</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>590</v>
+        <v>83</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>83</v>
@@ -15294,13 +15156,13 @@
         <v>83</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>583</v>
+        <v>286</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>83</v>
@@ -15312,27 +15174,27 @@
         <v>83</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>591</v>
+        <v>83</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>592</v>
+        <v>287</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>593</v>
+        <v>288</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP105" t="s" s="2">
-        <v>594</v>
+        <v>83</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>595</v>
+        <v>530</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>595</v>
+        <v>530</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15343,31 +15205,31 @@
         <v>81</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J106" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="I106" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J106" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="K106" t="s" s="2">
-        <v>596</v>
+        <v>217</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>597</v>
+        <v>312</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>598</v>
+        <v>313</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>599</v>
+        <v>314</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>600</v>
+        <v>315</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>83</v>
@@ -15416,13 +15278,13 @@
         <v>83</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>595</v>
+        <v>316</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>83</v>
@@ -15437,10 +15299,10 @@
         <v>83</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>601</v>
+        <v>317</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>602</v>
+        <v>318</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>83</v>
@@ -15451,10 +15313,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>603</v>
+        <v>531</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>603</v>
+        <v>531</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15480,15 +15342,17 @@
         <v>192</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>604</v>
+        <v>532</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>605</v>
+        <v>533</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="O107" s="2"/>
+        <v>534</v>
+      </c>
+      <c r="O107" t="s" s="2">
+        <v>535</v>
+      </c>
       <c r="P107" t="s" s="2">
         <v>83</v>
       </c>
@@ -15512,13 +15376,13 @@
         <v>83</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>207</v>
+        <v>341</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>607</v>
+        <v>536</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>608</v>
+        <v>537</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>83</v>
@@ -15536,7 +15400,7 @@
         <v>83</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>603</v>
+        <v>531</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
@@ -15545,7 +15409,7 @@
         <v>94</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>83</v>
+        <v>538</v>
       </c>
       <c r="AJ107" t="s" s="2">
         <v>106</v>
@@ -15554,38 +15418,38 @@
         <v>83</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>609</v>
+        <v>83</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>610</v>
+        <v>137</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>611</v>
+        <v>539</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP107" t="s" s="2">
-        <v>612</v>
+        <v>83</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>613</v>
+        <v>540</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>613</v>
+        <v>540</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>83</v>
+        <v>541</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H108" t="s" s="2">
         <v>83</v>
@@ -15600,16 +15464,16 @@
         <v>192</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>614</v>
+        <v>542</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>615</v>
+        <v>543</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>616</v>
+        <v>544</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>617</v>
+        <v>545</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>83</v>
@@ -15634,13 +15498,13 @@
         <v>83</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>207</v>
+        <v>341</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>618</v>
+        <v>546</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>619</v>
+        <v>547</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>83</v>
@@ -15658,13 +15522,13 @@
         <v>83</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>613</v>
+        <v>540</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI108" t="s" s="2">
         <v>83</v>
@@ -15676,27 +15540,27 @@
         <v>83</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>83</v>
+        <v>548</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>620</v>
+        <v>549</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>621</v>
+        <v>550</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>83</v>
+        <v>551</v>
       </c>
     </row>
-    <row r="109" hidden="true">
+    <row r="109">
       <c r="A109" t="s" s="2">
-        <v>622</v>
+        <v>552</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>622</v>
+        <v>552</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15707,10 +15571,10 @@
         <v>81</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H109" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I109" t="s" s="2">
         <v>83</v>
@@ -15719,18 +15583,20 @@
         <v>83</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>623</v>
+        <v>553</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>624</v>
+        <v>554</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>625</v>
+        <v>555</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="O109" s="2"/>
+        <v>556</v>
+      </c>
+      <c r="O109" t="s" s="2">
+        <v>557</v>
+      </c>
       <c r="P109" t="s" s="2">
         <v>83</v>
       </c>
@@ -15778,13 +15644,13 @@
         <v>83</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>622</v>
+        <v>552</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>83</v>
@@ -15796,27 +15662,27 @@
         <v>83</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>627</v>
+        <v>83</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>628</v>
+        <v>558</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>629</v>
+        <v>559</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP109" t="s" s="2">
-        <v>630</v>
+        <v>83</v>
       </c>
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>631</v>
+        <v>560</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>631</v>
+        <v>560</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15839,16 +15705,16 @@
         <v>83</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>632</v>
+        <v>192</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>633</v>
+        <v>561</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>634</v>
+        <v>562</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>635</v>
+        <v>563</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -15874,13 +15740,13 @@
         <v>83</v>
       </c>
       <c r="X110" t="s" s="2">
-        <v>83</v>
+        <v>207</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>83</v>
+        <v>564</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>83</v>
+        <v>565</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>83</v>
@@ -15898,7 +15764,7 @@
         <v>83</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>631</v>
+        <v>560</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>81</v>
@@ -15916,27 +15782,27 @@
         <v>83</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>636</v>
+        <v>566</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>637</v>
+        <v>567</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>638</v>
+        <v>568</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP110" t="s" s="2">
-        <v>639</v>
+        <v>569</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>640</v>
+        <v>570</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>640</v>
+        <v>570</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15947,7 +15813,7 @@
         <v>81</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>83</v>
@@ -15959,19 +15825,19 @@
         <v>83</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>641</v>
+        <v>192</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>642</v>
+        <v>571</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>643</v>
+        <v>572</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>644</v>
+        <v>573</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>645</v>
+        <v>574</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>83</v>
@@ -15996,13 +15862,13 @@
         <v>83</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>83</v>
+        <v>207</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>83</v>
+        <v>575</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>83</v>
+        <v>576</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>83</v>
@@ -16020,19 +15886,19 @@
         <v>83</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>640</v>
+        <v>570</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>646</v>
+        <v>106</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>83</v>
@@ -16041,10 +15907,10 @@
         <v>83</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>647</v>
+        <v>577</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>648</v>
+        <v>578</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>83</v>
@@ -16055,10 +15921,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>649</v>
+        <v>579</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>649</v>
+        <v>579</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16081,15 +15947,17 @@
         <v>83</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>217</v>
+        <v>580</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>218</v>
+        <v>581</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N112" s="2"/>
+        <v>582</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>583</v>
+      </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>83</v>
@@ -16138,7 +16006,7 @@
         <v>83</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>220</v>
+        <v>579</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>81</v>
@@ -16150,44 +16018,44 @@
         <v>83</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK112" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>83</v>
+        <v>584</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>83</v>
+        <v>585</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>221</v>
+        <v>586</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP112" t="s" s="2">
-        <v>83</v>
+        <v>587</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>650</v>
+        <v>588</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>650</v>
+        <v>588</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>83</v>
@@ -16199,16 +16067,16 @@
         <v>83</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>140</v>
+        <v>589</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>141</v>
+        <v>590</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>223</v>
+        <v>591</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>143</v>
+        <v>592</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -16258,49 +16126,49 @@
         <v>83</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>227</v>
+        <v>588</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>83</v>
+        <v>593</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>83</v>
+        <v>594</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>221</v>
+        <v>595</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP113" t="s" s="2">
-        <v>83</v>
+        <v>596</v>
       </c>
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>651</v>
+        <v>597</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>651</v>
+        <v>597</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>652</v>
+        <v>83</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
@@ -16313,25 +16181,25 @@
         <v>83</v>
       </c>
       <c r="I114" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J114" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>140</v>
+        <v>598</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>653</v>
+        <v>599</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>654</v>
+        <v>600</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>143</v>
+        <v>601</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>149</v>
+        <v>602</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>83</v>
@@ -16380,7 +16248,7 @@
         <v>83</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>655</v>
+        <v>597</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>81</v>
@@ -16392,7 +16260,7 @@
         <v>83</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>145</v>
+        <v>603</v>
       </c>
       <c r="AK114" t="s" s="2">
         <v>83</v>
@@ -16401,10 +16269,10 @@
         <v>83</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>83</v>
+        <v>604</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>137</v>
+        <v>605</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>83</v>
@@ -16415,10 +16283,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>656</v>
+        <v>606</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>656</v>
+        <v>606</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16441,13 +16309,13 @@
         <v>83</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>657</v>
+        <v>217</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>658</v>
+        <v>218</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>659</v>
+        <v>219</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -16498,7 +16366,7 @@
         <v>83</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>656</v>
+        <v>220</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>81</v>
@@ -16507,10 +16375,10 @@
         <v>94</v>
       </c>
       <c r="AI115" t="s" s="2">
-        <v>660</v>
+        <v>83</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>83</v>
@@ -16519,10 +16387,10 @@
         <v>83</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>661</v>
+        <v>83</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>662</v>
+        <v>221</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>83</v>
@@ -16533,21 +16401,21 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>663</v>
+        <v>607</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>663</v>
+        <v>607</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>83</v>
@@ -16559,15 +16427,17 @@
         <v>83</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>657</v>
+        <v>140</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>664</v>
+        <v>141</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="N116" s="2"/>
+        <v>223</v>
+      </c>
+      <c r="N116" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
         <v>83</v>
@@ -16616,19 +16486,19 @@
         <v>83</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>663</v>
+        <v>227</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI116" t="s" s="2">
-        <v>660</v>
+        <v>83</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK116" t="s" s="2">
         <v>83</v>
@@ -16637,10 +16507,10 @@
         <v>83</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>661</v>
+        <v>83</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>666</v>
+        <v>221</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>83</v>
@@ -16651,45 +16521,45 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>667</v>
+        <v>608</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>667</v>
+        <v>608</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>83</v>
+        <v>609</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I117" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J117" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>192</v>
+        <v>140</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>668</v>
+        <v>610</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>669</v>
+        <v>611</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>670</v>
+        <v>143</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>671</v>
+        <v>149</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>83</v>
@@ -16714,13 +16584,13 @@
         <v>83</v>
       </c>
       <c r="X117" t="s" s="2">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>672</v>
+        <v>83</v>
       </c>
       <c r="Z117" t="s" s="2">
-        <v>673</v>
+        <v>83</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>83</v>
@@ -16738,31 +16608,31 @@
         <v>83</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>667</v>
+        <v>612</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI117" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>674</v>
+        <v>83</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>675</v>
+        <v>83</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>593</v>
+        <v>137</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>83</v>
@@ -16773,10 +16643,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>676</v>
+        <v>613</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>676</v>
+        <v>613</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16787,7 +16657,7 @@
         <v>81</v>
       </c>
       <c r="G118" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H118" t="s" s="2">
         <v>83</v>
@@ -16799,20 +16669,16 @@
         <v>83</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>192</v>
+        <v>614</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>677</v>
+        <v>615</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>678</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>679</v>
-      </c>
-      <c r="O118" t="s" s="2">
-        <v>680</v>
-      </c>
+        <v>616</v>
+      </c>
+      <c r="N118" s="2"/>
+      <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
         <v>83</v>
       </c>
@@ -16836,13 +16702,13 @@
         <v>83</v>
       </c>
       <c r="X118" t="s" s="2">
-        <v>207</v>
+        <v>83</v>
       </c>
       <c r="Y118" t="s" s="2">
-        <v>681</v>
+        <v>83</v>
       </c>
       <c r="Z118" t="s" s="2">
-        <v>682</v>
+        <v>83</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>83</v>
@@ -16860,16 +16726,16 @@
         <v>83</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>676</v>
+        <v>613</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH118" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI118" t="s" s="2">
-        <v>83</v>
+        <v>617</v>
       </c>
       <c r="AJ118" t="s" s="2">
         <v>106</v>
@@ -16878,13 +16744,13 @@
         <v>83</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>674</v>
+        <v>83</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>675</v>
+        <v>618</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>593</v>
+        <v>619</v>
       </c>
       <c r="AO118" t="s" s="2">
         <v>83</v>
@@ -16895,10 +16761,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>683</v>
+        <v>620</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>683</v>
+        <v>620</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16921,18 +16787,16 @@
         <v>83</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>684</v>
+        <v>614</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>685</v>
+        <v>621</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>686</v>
+        <v>622</v>
       </c>
       <c r="N119" s="2"/>
-      <c r="O119" t="s" s="2">
-        <v>687</v>
-      </c>
+      <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>83</v>
       </c>
@@ -16980,7 +16844,7 @@
         <v>83</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>683</v>
+        <v>620</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>81</v>
@@ -16989,7 +16853,7 @@
         <v>94</v>
       </c>
       <c r="AI119" t="s" s="2">
-        <v>83</v>
+        <v>617</v>
       </c>
       <c r="AJ119" t="s" s="2">
         <v>106</v>
@@ -17001,10 +16865,10 @@
         <v>83</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>83</v>
+        <v>618</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>688</v>
+        <v>623</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>83</v>
@@ -17015,10 +16879,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>689</v>
+        <v>624</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>689</v>
+        <v>624</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17041,16 +16905,20 @@
         <v>83</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>217</v>
+        <v>192</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>690</v>
+        <v>625</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>691</v>
-      </c>
-      <c r="N120" s="2"/>
-      <c r="O120" s="2"/>
+        <v>626</v>
+      </c>
+      <c r="N120" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="O120" t="s" s="2">
+        <v>628</v>
+      </c>
       <c r="P120" t="s" s="2">
         <v>83</v>
       </c>
@@ -17074,13 +16942,13 @@
         <v>83</v>
       </c>
       <c r="X120" t="s" s="2">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="Y120" t="s" s="2">
-        <v>83</v>
+        <v>629</v>
       </c>
       <c r="Z120" t="s" s="2">
-        <v>83</v>
+        <v>630</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>83</v>
@@ -17098,7 +16966,7 @@
         <v>83</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>689</v>
+        <v>624</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>81</v>
@@ -17116,13 +16984,13 @@
         <v>83</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>83</v>
+        <v>631</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>661</v>
+        <v>632</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>692</v>
+        <v>550</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>83</v>
@@ -17133,10 +17001,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>693</v>
+        <v>633</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>693</v>
+        <v>633</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17156,21 +17024,23 @@
         <v>83</v>
       </c>
       <c r="J121" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>694</v>
+        <v>192</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>696</v>
+        <v>635</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>697</v>
-      </c>
-      <c r="O121" s="2"/>
+        <v>636</v>
+      </c>
+      <c r="O121" t="s" s="2">
+        <v>637</v>
+      </c>
       <c r="P121" t="s" s="2">
         <v>83</v>
       </c>
@@ -17194,13 +17064,13 @@
         <v>83</v>
       </c>
       <c r="X121" t="s" s="2">
-        <v>83</v>
+        <v>207</v>
       </c>
       <c r="Y121" t="s" s="2">
-        <v>83</v>
+        <v>638</v>
       </c>
       <c r="Z121" t="s" s="2">
-        <v>83</v>
+        <v>639</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>83</v>
@@ -17218,7 +17088,7 @@
         <v>83</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>693</v>
+        <v>633</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>81</v>
@@ -17236,13 +17106,13 @@
         <v>83</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>83</v>
+        <v>631</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>698</v>
+        <v>632</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>699</v>
+        <v>550</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>83</v>
@@ -17253,10 +17123,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>700</v>
+        <v>640</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>700</v>
+        <v>640</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17267,7 +17137,7 @@
         <v>81</v>
       </c>
       <c r="G122" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H122" t="s" s="2">
         <v>83</v>
@@ -17276,21 +17146,21 @@
         <v>83</v>
       </c>
       <c r="J122" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>701</v>
+        <v>641</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>702</v>
+        <v>642</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>703</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>704</v>
-      </c>
-      <c r="O122" s="2"/>
+        <v>643</v>
+      </c>
+      <c r="N122" s="2"/>
+      <c r="O122" t="s" s="2">
+        <v>644</v>
+      </c>
       <c r="P122" t="s" s="2">
         <v>83</v>
       </c>
@@ -17338,13 +17208,13 @@
         <v>83</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>700</v>
+        <v>640</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH122" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI122" t="s" s="2">
         <v>83</v>
@@ -17359,10 +17229,10 @@
         <v>83</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>698</v>
+        <v>83</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>705</v>
+        <v>645</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>83</v>
@@ -17373,10 +17243,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>706</v>
+        <v>646</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>706</v>
+        <v>646</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17387,7 +17257,7 @@
         <v>81</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H123" t="s" s="2">
         <v>83</v>
@@ -17396,23 +17266,19 @@
         <v>83</v>
       </c>
       <c r="J123" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>641</v>
+        <v>217</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>707</v>
+        <v>647</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>708</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>709</v>
-      </c>
-      <c r="O123" t="s" s="2">
-        <v>710</v>
-      </c>
+        <v>648</v>
+      </c>
+      <c r="N123" s="2"/>
+      <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
         <v>83</v>
       </c>
@@ -17460,13 +17326,13 @@
         <v>83</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>706</v>
+        <v>646</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH123" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI123" t="s" s="2">
         <v>83</v>
@@ -17481,10 +17347,10 @@
         <v>83</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>711</v>
+        <v>618</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>712</v>
+        <v>649</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>83</v>
@@ -17495,10 +17361,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>713</v>
+        <v>650</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>713</v>
+        <v>650</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17509,7 +17375,7 @@
         <v>81</v>
       </c>
       <c r="G124" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H124" t="s" s="2">
         <v>83</v>
@@ -17518,18 +17384,20 @@
         <v>83</v>
       </c>
       <c r="J124" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>217</v>
+        <v>651</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>218</v>
+        <v>652</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N124" s="2"/>
+        <v>653</v>
+      </c>
+      <c r="N124" t="s" s="2">
+        <v>654</v>
+      </c>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
         <v>83</v>
@@ -17578,19 +17446,19 @@
         <v>83</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>220</v>
+        <v>650</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH124" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI124" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK124" t="s" s="2">
         <v>83</v>
@@ -17599,10 +17467,10 @@
         <v>83</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>83</v>
+        <v>655</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>221</v>
+        <v>656</v>
       </c>
       <c r="AO124" t="s" s="2">
         <v>83</v>
@@ -17613,14 +17481,14 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>714</v>
+        <v>657</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>714</v>
+        <v>657</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
@@ -17636,19 +17504,19 @@
         <v>83</v>
       </c>
       <c r="J125" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>140</v>
+        <v>658</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>141</v>
+        <v>659</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>223</v>
+        <v>660</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>143</v>
+        <v>661</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -17698,7 +17566,7 @@
         <v>83</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>227</v>
+        <v>657</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>81</v>
@@ -17710,7 +17578,7 @@
         <v>83</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK125" t="s" s="2">
         <v>83</v>
@@ -17719,10 +17587,10 @@
         <v>83</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>83</v>
+        <v>655</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>221</v>
+        <v>662</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>83</v>
@@ -17733,14 +17601,14 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>715</v>
+        <v>663</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>715</v>
+        <v>663</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
-        <v>652</v>
+        <v>83</v>
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
@@ -17753,25 +17621,25 @@
         <v>83</v>
       </c>
       <c r="I126" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J126" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>140</v>
+        <v>598</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>653</v>
+        <v>664</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>654</v>
+        <v>665</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>143</v>
+        <v>666</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>149</v>
+        <v>667</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>83</v>
@@ -17820,7 +17688,7 @@
         <v>83</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>655</v>
+        <v>663</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>81</v>
@@ -17832,7 +17700,7 @@
         <v>83</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK126" t="s" s="2">
         <v>83</v>
@@ -17841,10 +17709,10 @@
         <v>83</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>83</v>
+        <v>668</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>137</v>
+        <v>669</v>
       </c>
       <c r="AO126" t="s" s="2">
         <v>83</v>
@@ -17855,10 +17723,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>716</v>
+        <v>670</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>716</v>
+        <v>670</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17866,7 +17734,7 @@
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G127" t="s" s="2">
         <v>94</v>
@@ -17878,23 +17746,19 @@
         <v>83</v>
       </c>
       <c r="J127" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>717</v>
+        <v>218</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>718</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>719</v>
-      </c>
-      <c r="O127" t="s" s="2">
-        <v>206</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="N127" s="2"/>
+      <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
         <v>83</v>
       </c>
@@ -17918,13 +17782,13 @@
         <v>83</v>
       </c>
       <c r="X127" t="s" s="2">
-        <v>207</v>
+        <v>83</v>
       </c>
       <c r="Y127" t="s" s="2">
-        <v>208</v>
+        <v>83</v>
       </c>
       <c r="Z127" t="s" s="2">
-        <v>209</v>
+        <v>83</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>83</v>
@@ -17942,10 +17806,10 @@
         <v>83</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>716</v>
+        <v>220</v>
       </c>
       <c r="AG127" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH127" t="s" s="2">
         <v>94</v>
@@ -17954,22 +17818,22 @@
         <v>83</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK127" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>720</v>
+        <v>83</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>212</v>
+        <v>83</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="AO127" t="s" s="2">
-        <v>214</v>
+        <v>83</v>
       </c>
       <c r="AP127" t="s" s="2">
         <v>83</v>
@@ -17977,21 +17841,21 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>721</v>
+        <v>671</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>721</v>
+        <v>671</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G128" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H128" t="s" s="2">
         <v>83</v>
@@ -18000,23 +17864,21 @@
         <v>83</v>
       </c>
       <c r="J128" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>511</v>
+        <v>140</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>722</v>
+        <v>141</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>513</v>
+        <v>223</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>723</v>
-      </c>
-      <c r="O128" t="s" s="2">
-        <v>515</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
         <v>83</v>
       </c>
@@ -18064,80 +17926,80 @@
         <v>83</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>721</v>
+        <v>227</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH128" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI128" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK128" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>724</v>
+        <v>83</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>519</v>
+        <v>83</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>520</v>
+        <v>221</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP128" t="s" s="2">
-        <v>521</v>
+        <v>83</v>
       </c>
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>725</v>
+        <v>672</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>725</v>
+        <v>672</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
-        <v>83</v>
+        <v>609</v>
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G129" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H129" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I129" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J129" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>192</v>
+        <v>140</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>726</v>
+        <v>610</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>727</v>
+        <v>611</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>728</v>
+        <v>143</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>578</v>
+        <v>149</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>83</v>
@@ -18162,13 +18024,13 @@
         <v>83</v>
       </c>
       <c r="X129" t="s" s="2">
-        <v>341</v>
+        <v>83</v>
       </c>
       <c r="Y129" t="s" s="2">
-        <v>579</v>
+        <v>83</v>
       </c>
       <c r="Z129" t="s" s="2">
-        <v>580</v>
+        <v>83</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>83</v>
@@ -18186,19 +18048,19 @@
         <v>83</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>725</v>
+        <v>612</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH129" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI129" t="s" s="2">
-        <v>581</v>
+        <v>83</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK129" t="s" s="2">
         <v>83</v>
@@ -18207,10 +18069,10 @@
         <v>83</v>
       </c>
       <c r="AM129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN129" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AN129" t="s" s="2">
-        <v>582</v>
       </c>
       <c r="AO129" t="s" s="2">
         <v>83</v>
@@ -18221,21 +18083,21 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>729</v>
+        <v>673</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>729</v>
+        <v>673</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>584</v>
+        <v>83</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G130" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H130" t="s" s="2">
         <v>83</v>
@@ -18244,22 +18106,22 @@
         <v>83</v>
       </c>
       <c r="J130" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K130" t="s" s="2">
         <v>192</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>585</v>
+        <v>674</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>586</v>
+        <v>675</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>587</v>
+        <v>676</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>588</v>
+        <v>206</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>83</v>
@@ -18284,13 +18146,13 @@
         <v>83</v>
       </c>
       <c r="X130" t="s" s="2">
-        <v>341</v>
+        <v>207</v>
       </c>
       <c r="Y130" t="s" s="2">
-        <v>589</v>
+        <v>208</v>
       </c>
       <c r="Z130" t="s" s="2">
-        <v>590</v>
+        <v>209</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>83</v>
@@ -18308,13 +18170,13 @@
         <v>83</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>729</v>
+        <v>673</v>
       </c>
       <c r="AG130" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH130" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI130" t="s" s="2">
         <v>83</v>
@@ -18326,27 +18188,27 @@
         <v>83</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>591</v>
+        <v>677</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>592</v>
+        <v>212</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>593</v>
+        <v>213</v>
       </c>
       <c r="AO130" t="s" s="2">
-        <v>83</v>
+        <v>214</v>
       </c>
       <c r="AP130" t="s" s="2">
-        <v>594</v>
+        <v>83</v>
       </c>
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>730</v>
+        <v>678</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>730</v>
+        <v>678</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18357,7 +18219,7 @@
         <v>81</v>
       </c>
       <c r="G131" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H131" t="s" s="2">
         <v>83</v>
@@ -18366,22 +18228,22 @@
         <v>83</v>
       </c>
       <c r="J131" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>84</v>
+        <v>679</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>731</v>
+        <v>680</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>732</v>
+        <v>511</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>644</v>
+        <v>681</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>645</v>
+        <v>513</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>83</v>
@@ -18430,13 +18292,13 @@
         <v>83</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>730</v>
+        <v>678</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH131" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI131" t="s" s="2">
         <v>83</v>
@@ -18448,23 +18310,389 @@
         <v>83</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>83</v>
+        <v>682</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>647</v>
+        <v>516</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>648</v>
+        <v>517</v>
       </c>
       <c r="AO131" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP131" t="s" s="2">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="132" hidden="true">
+      <c r="A132" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="B132" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="C132" s="2"/>
+      <c r="D132" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E132" s="2"/>
+      <c r="F132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G132" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H132" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I132" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J132" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K132" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L132" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="M132" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="N132" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="O132" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="P132" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q132" s="2"/>
+      <c r="R132" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S132" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T132" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U132" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V132" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W132" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X132" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="Y132" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="Z132" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="AA132" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB132" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC132" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD132" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE132" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF132" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="AG132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH132" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI132" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="AJ132" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK132" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL132" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM132" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AN132" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="AO132" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP132" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="133" hidden="true">
+      <c r="A133" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="B133" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="C133" s="2"/>
+      <c r="D133" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="E133" s="2"/>
+      <c r="F133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G133" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H133" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I133" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J133" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K133" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L133" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="M133" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="N133" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="O133" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="P133" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q133" s="2"/>
+      <c r="R133" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S133" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T133" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U133" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V133" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W133" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X133" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="Y133" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="Z133" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="AA133" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB133" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC133" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD133" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE133" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF133" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="AG133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH133" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI133" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ133" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK133" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL133" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="AM133" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="AN133" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="AO133" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP133" t="s" s="2">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="134" hidden="true">
+      <c r="A134" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="B134" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="C134" s="2"/>
+      <c r="D134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E134" s="2"/>
+      <c r="F134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G134" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K134" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L134" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="M134" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="N134" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="O134" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="P134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q134" s="2"/>
+      <c r="R134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF134" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="AG134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH134" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ134" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM134" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="AN134" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="AO134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP134" t="s" s="2">
         <v>83</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP131">
+  <autoFilter ref="A1:AP134">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -18474,7 +18702,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI130">
+  <conditionalFormatting sqref="A2:AI133">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/testbuild/StructureDefinition-vkp-Observation-CFSscore.xlsx
+++ b/testbuild/StructureDefinition-vkp-Observation-CFSscore.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-02T09:03:30+00:00</t>
+    <t>2026-10-02T10:19:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1453,9 +1453,9 @@
     <t>When the perfomer is an identified person, otherwise use CareTeam, PractitionerRole etc.</t>
   </si>
   <si>
-    <t>Reference to the person that performed the observation, identified by Norwegian national id number (Fødselsnummer).
+    <t>Reference to the person that performed the observation. The person is identified by Norwegian national id number (Fødselsnummer).
 A link to a resource representing the person or the group to whom the medication will be given.
-VKP always references a Practitioner Resource using a norwegian national id number (Fødselsnummer or DNR) in a logical identifier in the practitioner.identifier element.
+VKP always references a Practitioner Resource using a norwegian national id number (Fødselsnummer) in a logical identifier in the practitioner.identifier element.
 The Name of the practitioner should be given in the performer.display element.
 Example:
 ~~~~

--- a/testbuild/StructureDefinition-vkp-Observation-CFSscore.xlsx
+++ b/testbuild/StructureDefinition-vkp-Observation-CFSscore.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-02T10:19:39+00:00</t>
+    <t>2026-10-02T10:27:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
